--- a/dataset_agreed/saved_models/hyperparameter_optimized_runs/pointcloud_HPO_run_2/epoch_40/per_file_predictions_epoch_40.xlsx
+++ b/dataset_agreed/saved_models/hyperparameter_optimized_runs/pointcloud_HPO_run_2/epoch_40/per_file_predictions_epoch_40.xlsx
@@ -808,769 +808,769 @@
     <t>0,1,1,0</t>
   </si>
   <si>
-    <t>0.9338,0.0494,0.0045,0.0012</t>
-  </si>
-  <si>
-    <t>0.7819,0.1299,0.0354,0.0105</t>
-  </si>
-  <si>
-    <t>0.7526,0.2536,0.0135,0.0026</t>
-  </si>
-  <si>
-    <t>0.9166,0.0336,0.0093,0.0112</t>
-  </si>
-  <si>
-    <t>0.7064,0.3323,0.0035,0.0015</t>
-  </si>
-  <si>
-    <t>0.8207,0.1261,0.0010,0.0020</t>
-  </si>
-  <si>
-    <t>0.5639,0.4996,0.0089,0.0019</t>
-  </si>
-  <si>
-    <t>0.7808,0.2485,0.0155,0.0025</t>
-  </si>
-  <si>
-    <t>0.7474,0.3433,0.0038,0.0010</t>
-  </si>
-  <si>
-    <t>0.5889,0.5155,0.0126,0.0020</t>
-  </si>
-  <si>
-    <t>0.6432,0.3992,0.0038,0.0013</t>
-  </si>
-  <si>
-    <t>0.3319,0.7625,0.0138,0.0012</t>
-  </si>
-  <si>
-    <t>0.9751,0.0079,0.0091,0.0003</t>
-  </si>
-  <si>
-    <t>0.6705,0.1775,0.1242,0.0042</t>
-  </si>
-  <si>
-    <t>0.9621,0.0159,0.0170,0.0005</t>
-  </si>
-  <si>
-    <t>0.9742,0.0046,0.0224,0.0009</t>
-  </si>
-  <si>
-    <t>0.8819,0.1092,0.0125,0.0012</t>
-  </si>
-  <si>
-    <t>0.3970,0.7734,0.0047,0.0002</t>
-  </si>
-  <si>
-    <t>0.7069,0.4621,0.0041,0.0003</t>
-  </si>
-  <si>
-    <t>0.5082,0.6378,0.0050,0.0004</t>
-  </si>
-  <si>
-    <t>0.0900,0.9415,0.0054,0.0003</t>
-  </si>
-  <si>
-    <t>0.0864,0.9499,0.0026,0.0002</t>
-  </si>
-  <si>
-    <t>0.9074,0.0240,0.0497,0.0008</t>
-  </si>
-  <si>
-    <t>0.9658,0.0116,0.0151,0.0008</t>
-  </si>
-  <si>
-    <t>0.8988,0.0111,0.1271,0.0019</t>
-  </si>
-  <si>
-    <t>0.9340,0.0322,0.0190,0.0004</t>
-  </si>
-  <si>
-    <t>0.9471,0.0094,0.0603,0.0012</t>
-  </si>
-  <si>
-    <t>0.9028,0.0207,0.0833,0.0020</t>
-  </si>
-  <si>
-    <t>0.2187,0.0100,0.8716,0.0009</t>
-  </si>
-  <si>
-    <t>0.8088,0.2537,0.0062,0.0003</t>
-  </si>
-  <si>
-    <t>0.8559,0.1281,0.0227,0.0015</t>
-  </si>
-  <si>
-    <t>0.2439,0.0493,0.8246,0.0008</t>
-  </si>
-  <si>
-    <t>0.7648,0.2711,0.0103,0.0002</t>
-  </si>
-  <si>
-    <t>0.8893,0.0964,0.0086,0.0013</t>
-  </si>
-  <si>
-    <t>0.8921,0.1392,0.0056,0.0010</t>
-  </si>
-  <si>
-    <t>0.6733,0.4797,0.0068,0.0009</t>
-  </si>
-  <si>
-    <t>0.9596,0.0545,0.0025,0.0001</t>
-  </si>
-  <si>
-    <t>0.9030,0.0150,0.1246,0.0035</t>
-  </si>
-  <si>
-    <t>0.9800,0.0014,0.0372,0.0006</t>
-  </si>
-  <si>
-    <t>0.9608,0.0026,0.0593,0.0004</t>
-  </si>
-  <si>
-    <t>0.9801,0.0036,0.0110,0.0003</t>
-  </si>
-  <si>
-    <t>0.9626,0.0018,0.0591,0.0005</t>
-  </si>
-  <si>
-    <t>0.1505,0.2029,0.3515,0.0018</t>
-  </si>
-  <si>
-    <t>0.9486,0.0022,0.1054,0.0003</t>
-  </si>
-  <si>
-    <t>0.9523,0.0306,0.0044,0.0013</t>
-  </si>
-  <si>
-    <t>0.7920,0.2470,0.0082,0.0001</t>
-  </si>
-  <si>
-    <t>0.8787,0.0647,0.0247,0.0002</t>
-  </si>
-  <si>
-    <t>0.9220,0.0927,0.0031,0.0001</t>
-  </si>
-  <si>
-    <t>0.1043,0.0677,0.9171,0.0047</t>
-  </si>
-  <si>
-    <t>0.4802,0.0249,0.6146,0.0098</t>
-  </si>
-  <si>
-    <t>0.9496,0.0020,0.1041,0.0007</t>
-  </si>
-  <si>
-    <t>0.9213,0.0141,0.0740,0.0042</t>
-  </si>
-  <si>
-    <t>0.6146,0.0164,0.5143,0.0008</t>
-  </si>
-  <si>
-    <t>0.9567,0.0032,0.0704,0.0003</t>
-  </si>
-  <si>
-    <t>0.8142,0.2553,0.0040,0.0009</t>
-  </si>
-  <si>
-    <t>0.8675,0.1270,0.0014,0.0014</t>
-  </si>
-  <si>
-    <t>0.8404,0.1209,0.0043,0.0051</t>
-  </si>
-  <si>
-    <t>0.1588,0.6850,0.4328,0.0064</t>
-  </si>
-  <si>
-    <t>0.9403,0.0663,0.0017,0.0005</t>
-  </si>
-  <si>
-    <t>0.9574,0.0328,0.0011,0.0015</t>
-  </si>
-  <si>
-    <t>0.7467,0.3348,0.0049,0.0007</t>
-  </si>
-  <si>
-    <t>0.1625,0.4167,0.7791,0.0043</t>
-  </si>
-  <si>
-    <t>0.7945,0.0015,0.3902,0.0013</t>
-  </si>
-  <si>
-    <t>0.7293,0.0110,0.3871,0.0016</t>
-  </si>
-  <si>
-    <t>0.1591,0.5544,0.5906,0.0019</t>
-  </si>
-  <si>
-    <t>0.4497,0.0022,0.7997,0.0006</t>
-  </si>
-  <si>
-    <t>0.5710,0.5595,0.0074,0.0002</t>
-  </si>
-  <si>
-    <t>0.5877,0.5983,0.0019,0.0001</t>
-  </si>
-  <si>
-    <t>0.8000,0.2455,0.0144,0.0005</t>
-  </si>
-  <si>
-    <t>0.9018,0.0660,0.0155,0.0011</t>
-  </si>
-  <si>
-    <t>0.3266,0.6565,0.1004,0.0047</t>
-  </si>
-  <si>
-    <t>0.4264,0.2864,0.2387,0.0016</t>
-  </si>
-  <si>
-    <t>0.9660,0.0029,0.0508,0.0002</t>
-  </si>
-  <si>
-    <t>0.1923,0.7330,0.0760,0.0004</t>
-  </si>
-  <si>
-    <t>0.6379,0.2133,0.0988,0.0002</t>
-  </si>
-  <si>
-    <t>0.8755,0.0529,0.0207,0.0164</t>
-  </si>
-  <si>
-    <t>0.8201,0.0888,0.0321,0.0273</t>
-  </si>
-  <si>
-    <t>0.9497,0.0175,0.0066,0.0037</t>
-  </si>
-  <si>
-    <t>0.8721,0.0735,0.0113,0.0084</t>
-  </si>
-  <si>
-    <t>0.9402,0.0289,0.0092,0.0033</t>
-  </si>
-  <si>
-    <t>0.8936,0.0426,0.0228,0.0115</t>
-  </si>
-  <si>
-    <t>0.9214,0.0233,0.0234,0.0001</t>
-  </si>
-  <si>
-    <t>0.2213,0.0335,0.8167,0.0042</t>
-  </si>
-  <si>
-    <t>0.5664,0.0643,0.4112,0.0006</t>
-  </si>
-  <si>
-    <t>0.9704,0.0016,0.0672,0.0001</t>
-  </si>
-  <si>
-    <t>0.4241,0.2610,0.1850,0.0005</t>
-  </si>
-  <si>
-    <t>0.9694,0.0076,0.0175,0.0002</t>
-  </si>
-  <si>
-    <t>0.7642,0.2993,0.0049,0.0011</t>
-  </si>
-  <si>
-    <t>0.8990,0.1328,0.0016,0.0007</t>
-  </si>
-  <si>
-    <t>0.7088,0.3502,0.0058,0.0019</t>
-  </si>
-  <si>
-    <t>0.7913,0.2634,0.0060,0.0014</t>
-  </si>
-  <si>
-    <t>0.9573,0.0366,0.0005,0.0007</t>
-  </si>
-  <si>
-    <t>0.8246,0.0984,0.0010,0.0022</t>
-  </si>
-  <si>
-    <t>0.6129,0.5207,0.0025,0.0007</t>
-  </si>
-  <si>
-    <t>0.5009,0.6263,0.0063,0.0009</t>
-  </si>
-  <si>
-    <t>0.8930,0.1170,0.0020,0.0010</t>
-  </si>
-  <si>
-    <t>0.8528,0.1746,0.0033,0.0010</t>
-  </si>
-  <si>
-    <t>0.8445,0.1519,0.0033,0.0011</t>
-  </si>
-  <si>
-    <t>0.8256,0.1142,0.0019,0.0035</t>
-  </si>
-  <si>
-    <t>0.8849,0.1059,0.0013,0.0012</t>
-  </si>
-  <si>
-    <t>0.6919,0.3904,0.0083,0.0018</t>
-  </si>
-  <si>
-    <t>0.7975,0.3096,0.0038,0.0008</t>
-  </si>
-  <si>
-    <t>0.8797,0.1067,0.0009,0.0010</t>
-  </si>
-  <si>
-    <t>0.4146,0.0194,0.7096,0.0029</t>
-  </si>
-  <si>
-    <t>0.8948,0.0431,0.0585,0.0022</t>
-  </si>
-  <si>
-    <t>0.9832,0.0037,0.0087,0.0003</t>
-  </si>
-  <si>
-    <t>0.8557,0.0316,0.1264,0.0012</t>
-  </si>
-  <si>
-    <t>0.0538,0.9460,0.0063,0.0011</t>
-  </si>
-  <si>
-    <t>0.0255,0.9746,0.0043,0.0003</t>
-  </si>
-  <si>
-    <t>0.5279,0.5818,0.0088,0.0005</t>
-  </si>
-  <si>
-    <t>0.5212,0.5821,0.0160,0.0011</t>
-  </si>
-  <si>
-    <t>0.6873,0.4303,0.0051,0.0003</t>
-  </si>
-  <si>
-    <t>0.2128,0.8826,0.0033,0.0003</t>
-  </si>
-  <si>
-    <t>0.9162,0.1009,0.0015,0.0007</t>
-  </si>
-  <si>
-    <t>0.7286,0.1874,0.0592,0.0014</t>
-  </si>
-  <si>
-    <t>0.9599,0.0074,0.0275,0.0026</t>
-  </si>
-  <si>
-    <t>0.9880,0.0026,0.0053,0.0003</t>
-  </si>
-  <si>
-    <t>0.9439,0.0246,0.0201,0.0014</t>
-  </si>
-  <si>
-    <t>0.9005,0.0643,0.0176,0.0043</t>
-  </si>
-  <si>
-    <t>0.8973,0.1230,0.0035,0.0001</t>
-  </si>
-  <si>
-    <t>0.9619,0.0314,0.0045,0.0004</t>
-  </si>
-  <si>
-    <t>0.8365,0.1485,0.0249,0.0008</t>
-  </si>
-  <si>
-    <t>0.7250,0.0608,0.0805,0.0002</t>
-  </si>
-  <si>
-    <t>0.9690,0.0319,0.0021,0.0000</t>
-  </si>
-  <si>
-    <t>0.7576,0.3248,0.0026,0.0006</t>
-  </si>
-  <si>
-    <t>0.7828,0.2482,0.0095,0.0019</t>
-  </si>
-  <si>
-    <t>0.8471,0.1873,0.0057,0.0006</t>
-  </si>
-  <si>
-    <t>0.5188,0.5940,0.0059,0.0014</t>
-  </si>
-  <si>
-    <t>0.8549,0.1233,0.0044,0.0020</t>
-  </si>
-  <si>
-    <t>0.7800,0.3311,0.0039,0.0006</t>
-  </si>
-  <si>
-    <t>0.7702,0.2547,0.0163,0.0022</t>
-  </si>
-  <si>
-    <t>0.6499,0.4850,0.0097,0.0009</t>
-  </si>
-  <si>
-    <t>0.7230,0.3156,0.0147,0.0016</t>
-  </si>
-  <si>
-    <t>0.5923,0.5356,0.0228,0.0017</t>
-  </si>
-  <si>
-    <t>0.6780,0.1547,0.1304,0.0008</t>
-  </si>
-  <si>
-    <t>0.8559,0.0085,0.2540,0.0005</t>
-  </si>
-  <si>
-    <t>0.7395,0.0149,0.3802,0.0016</t>
-  </si>
-  <si>
-    <t>0.9496,0.0069,0.0448,0.0004</t>
-  </si>
-  <si>
-    <t>0.9529,0.0181,0.0141,0.0015</t>
-  </si>
-  <si>
-    <t>0.9040,0.0604,0.0264,0.0006</t>
-  </si>
-  <si>
-    <t>0.9321,0.0145,0.0513,0.0031</t>
-  </si>
-  <si>
-    <t>0.9421,0.0172,0.0210,0.0006</t>
-  </si>
-  <si>
-    <t>0.9379,0.0269,0.0134,0.0037</t>
-  </si>
-  <si>
-    <t>0.8548,0.0273,0.0130,0.0580</t>
-  </si>
-  <si>
-    <t>0.8457,0.0553,0.0306,0.0349</t>
-  </si>
-  <si>
-    <t>0.9025,0.0442,0.0128,0.0066</t>
-  </si>
-  <si>
-    <t>0.5248,0.0914,0.3019,0.0007</t>
-  </si>
-  <si>
-    <t>0.8872,0.1201,0.0052,0.0019</t>
-  </si>
-  <si>
-    <t>0.6678,0.4309,0.0102,0.0009</t>
-  </si>
-  <si>
-    <t>0.8897,0.1130,0.0020,0.0013</t>
-  </si>
-  <si>
-    <t>0.9403,0.0673,0.0024,0.0005</t>
-  </si>
-  <si>
-    <t>0.7424,0.3323,0.0117,0.0009</t>
-  </si>
-  <si>
-    <t>0.8313,0.1643,0.0126,0.0015</t>
-  </si>
-  <si>
-    <t>0.8634,0.0989,0.0036,0.0035</t>
-  </si>
-  <si>
-    <t>0.6686,0.1367,0.2810,0.0695</t>
-  </si>
-  <si>
-    <t>0.9283,0.0664,0.0032,0.0010</t>
-  </si>
-  <si>
-    <t>0.7808,0.1919,0.0079,0.0044</t>
-  </si>
-  <si>
-    <t>0.7567,0.3095,0.0098,0.0007</t>
-  </si>
-  <si>
-    <t>0.9328,0.0887,0.0018,0.0002</t>
-  </si>
-  <si>
-    <t>0.8225,0.2632,0.0019,0.0003</t>
-  </si>
-  <si>
-    <t>0.9401,0.0630,0.0041,0.0003</t>
-  </si>
-  <si>
-    <t>0.8234,0.2155,0.0129,0.0010</t>
-  </si>
-  <si>
-    <t>0.9565,0.0521,0.0014,0.0004</t>
-  </si>
-  <si>
-    <t>0.7095,0.3535,0.0140,0.0022</t>
-  </si>
-  <si>
-    <t>0.9531,0.0394,0.0014,0.0013</t>
-  </si>
-  <si>
-    <t>0.7332,0.3769,0.0041,0.0008</t>
-  </si>
-  <si>
-    <t>0.6911,0.3197,0.0074,0.0030</t>
-  </si>
-  <si>
-    <t>0.8562,0.1170,0.0025,0.0017</t>
-  </si>
-  <si>
-    <t>0.6244,0.4386,0.0132,0.0021</t>
-  </si>
-  <si>
-    <t>0.7054,0.3190,0.0042,0.0025</t>
-  </si>
-  <si>
-    <t>0.9320,0.0387,0.0006,0.0016</t>
-  </si>
-  <si>
-    <t>0.8906,0.1081,0.0027,0.0009</t>
-  </si>
-  <si>
-    <t>0.8418,0.2063,0.0035,0.0005</t>
-  </si>
-  <si>
-    <t>0.7956,0.2903,0.0039,0.0004</t>
-  </si>
-  <si>
-    <t>0.8905,0.1110,0.0042,0.0011</t>
-  </si>
-  <si>
-    <t>0.7938,0.2859,0.0017,0.0005</t>
-  </si>
-  <si>
-    <t>0.6415,0.5162,0.0036,0.0004</t>
-  </si>
-  <si>
-    <t>0.6954,0.3977,0.0033,0.0010</t>
-  </si>
-  <si>
-    <t>0.8152,0.2411,0.0038,0.0006</t>
-  </si>
-  <si>
-    <t>0.0999,0.4860,0.2573,0.0004</t>
-  </si>
-  <si>
-    <t>0.8712,0.1379,0.0042,0.0011</t>
-  </si>
-  <si>
-    <t>0.3636,0.0393,0.7099,0.0024</t>
-  </si>
-  <si>
-    <t>0.8870,0.0114,0.1453,0.0016</t>
-  </si>
-  <si>
-    <t>0.9781,0.0037,0.0206,0.0006</t>
-  </si>
-  <si>
-    <t>0.0712,0.0237,0.9547,0.0010</t>
-  </si>
-  <si>
-    <t>0.5782,0.0102,0.6208,0.0013</t>
-  </si>
-  <si>
-    <t>0.9144,0.0069,0.1138,0.0007</t>
-  </si>
-  <si>
-    <t>0.9094,0.0126,0.1334,0.0009</t>
-  </si>
-  <si>
-    <t>0.9346,0.0337,0.0172,0.0004</t>
-  </si>
-  <si>
-    <t>0.6762,0.0091,0.5271,0.0019</t>
-  </si>
-  <si>
-    <t>0.9063,0.0471,0.0256,0.0010</t>
-  </si>
-  <si>
-    <t>0.9267,0.0440,0.0215,0.0005</t>
-  </si>
-  <si>
-    <t>0.7611,0.1756,0.0366,0.0011</t>
-  </si>
-  <si>
-    <t>0.8937,0.0514,0.0272,0.0003</t>
-  </si>
-  <si>
-    <t>0.6088,0.2850,0.1478,0.0130</t>
-  </si>
-  <si>
-    <t>0.7290,0.1685,0.0957,0.0051</t>
-  </si>
-  <si>
-    <t>0.7229,0.3369,0.0038,0.0010</t>
-  </si>
-  <si>
-    <t>0.6098,0.5645,0.0014,0.0005</t>
-  </si>
-  <si>
-    <t>0.5483,0.6117,0.0041,0.0005</t>
-  </si>
-  <si>
-    <t>0.9475,0.0357,0.0008,0.0011</t>
-  </si>
-  <si>
-    <t>0.7832,0.2700,0.0022,0.0007</t>
-  </si>
-  <si>
-    <t>0.7639,0.2014,0.0445,0.0020</t>
-  </si>
-  <si>
-    <t>0.8348,0.1214,0.0333,0.0016</t>
-  </si>
-  <si>
-    <t>0.9151,0.0463,0.0140,0.0016</t>
-  </si>
-  <si>
-    <t>0.8617,0.0499,0.0733,0.0018</t>
-  </si>
-  <si>
-    <t>0.8655,0.1044,0.0149,0.0021</t>
-  </si>
-  <si>
-    <t>0.4547,0.0342,0.5827,0.0038</t>
-  </si>
-  <si>
-    <t>0.9947,0.0009,0.0046,0.0001</t>
-  </si>
-  <si>
-    <t>0.9426,0.0136,0.0314,0.0004</t>
-  </si>
-  <si>
-    <t>0.9483,0.0023,0.1281,0.0003</t>
-  </si>
-  <si>
-    <t>0.9653,0.0015,0.0717,0.0005</t>
-  </si>
-  <si>
-    <t>0.7898,0.2588,0.0045,0.0015</t>
-  </si>
-  <si>
-    <t>0.5038,0.6195,0.0074,0.0009</t>
-  </si>
-  <si>
-    <t>0.7172,0.3316,0.0069,0.0020</t>
-  </si>
-  <si>
-    <t>0.8699,0.1803,0.0015,0.0005</t>
-  </si>
-  <si>
-    <t>0.7556,0.2808,0.0117,0.0017</t>
-  </si>
-  <si>
-    <t>0.9008,0.1130,0.0041,0.0013</t>
-  </si>
-  <si>
-    <t>0.8245,0.1904,0.0010,0.0007</t>
-  </si>
-  <si>
-    <t>0.7796,0.2854,0.0042,0.0009</t>
-  </si>
-  <si>
-    <t>0.7969,0.1436,0.0593,0.0026</t>
-  </si>
-  <si>
-    <t>0.6719,0.3345,0.0302,0.0011</t>
-  </si>
-  <si>
-    <t>0.6963,0.3590,0.0246,0.0020</t>
-  </si>
-  <si>
-    <t>0.7896,0.0205,0.2439,0.0010</t>
-  </si>
-  <si>
-    <t>0.5460,0.0156,0.5854,0.0010</t>
-  </si>
-  <si>
-    <t>0.4472,0.1621,0.3602,0.0023</t>
-  </si>
-  <si>
-    <t>0.1829,0.0076,0.9171,0.0005</t>
-  </si>
-  <si>
-    <t>0.9614,0.0034,0.0493,0.0010</t>
-  </si>
-  <si>
-    <t>0.1609,0.0139,0.8668,0.0032</t>
-  </si>
-  <si>
-    <t>0.9788,0.0022,0.0315,0.0002</t>
-  </si>
-  <si>
-    <t>0.7889,0.1562,0.0485,0.0012</t>
-  </si>
-  <si>
-    <t>0.9227,0.0313,0.0137,0.0020</t>
-  </si>
-  <si>
-    <t>0.9592,0.0207,0.0134,0.0007</t>
-  </si>
-  <si>
-    <t>0.9423,0.0231,0.0224,0.0004</t>
-  </si>
-  <si>
-    <t>0.2764,0.7926,0.0067,0.0010</t>
-  </si>
-  <si>
-    <t>0.6242,0.4895,0.0076,0.0011</t>
-  </si>
-  <si>
-    <t>0.6584,0.4476,0.0043,0.0009</t>
-  </si>
-  <si>
-    <t>0.6501,0.4342,0.0027,0.0011</t>
-  </si>
-  <si>
-    <t>0.9206,0.0526,0.0010,0.0019</t>
-  </si>
-  <si>
-    <t>0.8642,0.1841,0.0030,0.0005</t>
-  </si>
-  <si>
-    <t>0.7828,0.2888,0.0019,0.0007</t>
-  </si>
-  <si>
-    <t>0.7941,0.2296,0.0037,0.0018</t>
-  </si>
-  <si>
-    <t>0.9147,0.0188,0.0599,0.0004</t>
-  </si>
-  <si>
-    <t>0.5253,0.0046,0.6884,0.0008</t>
-  </si>
-  <si>
-    <t>0.7078,0.0068,0.3638,0.0005</t>
-  </si>
-  <si>
-    <t>0.9430,0.0178,0.0330,0.0004</t>
-  </si>
-  <si>
-    <t>0.6768,0.0036,0.5282,0.0006</t>
-  </si>
-  <si>
-    <t>0.9115,0.0268,0.0604,0.0029</t>
-  </si>
-  <si>
-    <t>0.9678,0.0102,0.0200,0.0005</t>
-  </si>
-  <si>
-    <t>0.9827,0.0019,0.0151,0.0006</t>
-  </si>
-  <si>
-    <t>0.8443,0.0515,0.0158,0.0233</t>
-  </si>
-  <si>
-    <t>0.9403,0.0137,0.0284,0.0068</t>
-  </si>
-  <si>
-    <t>0.9124,0.0401,0.0115,0.0082</t>
-  </si>
-  <si>
-    <t>0.8110,0.0667,0.0161,0.0253</t>
-  </si>
-  <si>
-    <t>0.8694,0.0205,0.0163,0.0603</t>
-  </si>
-  <si>
-    <t>0.9109,0.0650,0.0109,0.0019</t>
+    <t>0.8804,0.0931,0.0165,0.0020</t>
+  </si>
+  <si>
+    <t>0.8088,0.0735,0.0184,0.0271</t>
+  </si>
+  <si>
+    <t>0.8901,0.0648,0.0109,0.0049</t>
+  </si>
+  <si>
+    <t>0.8994,0.0709,0.0025,0.0019</t>
+  </si>
+  <si>
+    <t>0.7394,0.3220,0.0075,0.0018</t>
+  </si>
+  <si>
+    <t>0.7916,0.1884,0.0016,0.0015</t>
+  </si>
+  <si>
+    <t>0.8543,0.1778,0.0031,0.0011</t>
+  </si>
+  <si>
+    <t>0.4748,0.6612,0.0105,0.0013</t>
+  </si>
+  <si>
+    <t>0.8928,0.1235,0.0008,0.0005</t>
+  </si>
+  <si>
+    <t>0.8960,0.1476,0.0010,0.0004</t>
+  </si>
+  <si>
+    <t>0.9224,0.0787,0.0012,0.0013</t>
+  </si>
+  <si>
+    <t>0.5751,0.5712,0.0068,0.0009</t>
+  </si>
+  <si>
+    <t>0.8836,0.1153,0.0138,0.0003</t>
+  </si>
+  <si>
+    <t>0.9619,0.0143,0.0179,0.0005</t>
+  </si>
+  <si>
+    <t>0.8557,0.0420,0.1120,0.0018</t>
+  </si>
+  <si>
+    <t>0.8933,0.0461,0.0609,0.0026</t>
+  </si>
+  <si>
+    <t>0.9341,0.0401,0.0095,0.0007</t>
+  </si>
+  <si>
+    <t>0.3116,0.8463,0.0013,0.0000</t>
+  </si>
+  <si>
+    <t>0.2021,0.8744,0.0037,0.0006</t>
+  </si>
+  <si>
+    <t>0.7550,0.3006,0.0128,0.0011</t>
+  </si>
+  <si>
+    <t>0.3355,0.8339,0.0021,0.0002</t>
+  </si>
+  <si>
+    <t>0.5902,0.6109,0.0024,0.0001</t>
+  </si>
+  <si>
+    <t>0.9815,0.0031,0.0109,0.0004</t>
+  </si>
+  <si>
+    <t>0.9911,0.0007,0.0127,0.0001</t>
+  </si>
+  <si>
+    <t>0.9742,0.0034,0.0201,0.0003</t>
+  </si>
+  <si>
+    <t>0.9597,0.0068,0.0388,0.0003</t>
+  </si>
+  <si>
+    <t>0.9436,0.0221,0.0245,0.0009</t>
+  </si>
+  <si>
+    <t>0.8590,0.0266,0.1701,0.0022</t>
+  </si>
+  <si>
+    <t>0.2716,0.0146,0.8012,0.0034</t>
+  </si>
+  <si>
+    <t>0.9333,0.0834,0.0045,0.0003</t>
+  </si>
+  <si>
+    <t>0.9265,0.0548,0.0136,0.0009</t>
+  </si>
+  <si>
+    <t>0.0073,0.2470,0.9820,0.0110</t>
+  </si>
+  <si>
+    <t>0.3059,0.7344,0.0104,0.0001</t>
+  </si>
+  <si>
+    <t>0.7850,0.2143,0.0141,0.0028</t>
+  </si>
+  <si>
+    <t>0.6912,0.3333,0.0269,0.0027</t>
+  </si>
+  <si>
+    <t>0.8158,0.2656,0.0063,0.0006</t>
+  </si>
+  <si>
+    <t>0.9814,0.0163,0.0021,0.0001</t>
+  </si>
+  <si>
+    <t>0.8735,0.0494,0.0193,0.0002</t>
+  </si>
+  <si>
+    <t>0.9738,0.0021,0.0362,0.0004</t>
+  </si>
+  <si>
+    <t>0.9819,0.0017,0.0253,0.0003</t>
+  </si>
+  <si>
+    <t>0.9916,0.0012,0.0053,0.0001</t>
+  </si>
+  <si>
+    <t>0.8873,0.0021,0.2742,0.0005</t>
+  </si>
+  <si>
+    <t>0.7176,0.1257,0.0263,0.0002</t>
+  </si>
+  <si>
+    <t>0.9604,0.0028,0.0559,0.0002</t>
+  </si>
+  <si>
+    <t>0.8885,0.0900,0.0238,0.0011</t>
+  </si>
+  <si>
+    <t>0.9323,0.0597,0.0038,0.0002</t>
+  </si>
+  <si>
+    <t>0.8387,0.1493,0.0159,0.0005</t>
+  </si>
+  <si>
+    <t>0.9553,0.0309,0.0063,0.0001</t>
+  </si>
+  <si>
+    <t>0.2409,0.1122,0.6340,0.0021</t>
+  </si>
+  <si>
+    <t>0.2542,0.0552,0.7666,0.0015</t>
+  </si>
+  <si>
+    <t>0.9383,0.0043,0.1068,0.0017</t>
+  </si>
+  <si>
+    <t>0.7122,0.0090,0.4832,0.0018</t>
+  </si>
+  <si>
+    <t>0.8647,0.0044,0.2057,0.0003</t>
+  </si>
+  <si>
+    <t>0.6366,0.0140,0.3477,0.0004</t>
+  </si>
+  <si>
+    <t>0.8635,0.1179,0.0033,0.0020</t>
+  </si>
+  <si>
+    <t>0.9072,0.0845,0.0035,0.0015</t>
+  </si>
+  <si>
+    <t>0.8707,0.1313,0.0026,0.0012</t>
+  </si>
+  <si>
+    <t>0.6129,0.4749,0.0195,0.0011</t>
+  </si>
+  <si>
+    <t>0.8474,0.1189,0.0035,0.0030</t>
+  </si>
+  <si>
+    <t>0.7621,0.2363,0.0023,0.0017</t>
+  </si>
+  <si>
+    <t>0.9207,0.0789,0.0035,0.0011</t>
+  </si>
+  <si>
+    <t>0.5113,0.1439,0.4391,0.0028</t>
+  </si>
+  <si>
+    <t>0.3176,0.0217,0.8173,0.0011</t>
+  </si>
+  <si>
+    <t>0.6108,0.0127,0.5695,0.0030</t>
+  </si>
+  <si>
+    <t>0.6146,0.0763,0.1890,0.0005</t>
+  </si>
+  <si>
+    <t>0.2249,0.0141,0.8866,0.0006</t>
+  </si>
+  <si>
+    <t>0.6720,0.4471,0.0094,0.0002</t>
+  </si>
+  <si>
+    <t>0.4448,0.6816,0.0049,0.0001</t>
+  </si>
+  <si>
+    <t>0.9495,0.0366,0.0033,0.0012</t>
+  </si>
+  <si>
+    <t>0.9013,0.0950,0.0121,0.0006</t>
+  </si>
+  <si>
+    <t>0.1466,0.4336,0.2991,0.0044</t>
+  </si>
+  <si>
+    <t>0.8036,0.0109,0.3073,0.0007</t>
+  </si>
+  <si>
+    <t>0.9366,0.0047,0.1303,0.0005</t>
+  </si>
+  <si>
+    <t>0.0398,0.9503,0.0883,0.0005</t>
+  </si>
+  <si>
+    <t>0.0639,0.8993,0.0474,0.0001</t>
+  </si>
+  <si>
+    <t>0.8789,0.0527,0.0355,0.0111</t>
+  </si>
+  <si>
+    <t>0.9312,0.0200,0.0047,0.0110</t>
+  </si>
+  <si>
+    <t>0.9769,0.0067,0.0016,0.0024</t>
+  </si>
+  <si>
+    <t>0.9171,0.0375,0.0094,0.0089</t>
+  </si>
+  <si>
+    <t>0.9286,0.0203,0.0104,0.0145</t>
+  </si>
+  <si>
+    <t>0.9421,0.0123,0.0140,0.0092</t>
+  </si>
+  <si>
+    <t>0.7365,0.1989,0.0391,0.0007</t>
+  </si>
+  <si>
+    <t>0.5851,0.0079,0.5865,0.0022</t>
+  </si>
+  <si>
+    <t>0.7802,0.0302,0.3014,0.0019</t>
+  </si>
+  <si>
+    <t>0.8081,0.0295,0.1865,0.0009</t>
+  </si>
+  <si>
+    <t>0.7680,0.0691,0.1141,0.0014</t>
+  </si>
+  <si>
+    <t>0.4833,0.2292,0.0328,0.0001</t>
+  </si>
+  <si>
+    <t>0.4047,0.6621,0.0091,0.0022</t>
+  </si>
+  <si>
+    <t>0.9072,0.1088,0.0014,0.0004</t>
+  </si>
+  <si>
+    <t>0.6547,0.4343,0.0085,0.0014</t>
+  </si>
+  <si>
+    <t>0.8665,0.1013,0.0009,0.0017</t>
+  </si>
+  <si>
+    <t>0.7465,0.4035,0.0012,0.0004</t>
+  </si>
+  <si>
+    <t>0.5724,0.5479,0.0066,0.0010</t>
+  </si>
+  <si>
+    <t>0.9025,0.0884,0.0038,0.0019</t>
+  </si>
+  <si>
+    <t>0.7203,0.3770,0.0069,0.0013</t>
+  </si>
+  <si>
+    <t>0.6080,0.4077,0.0090,0.0044</t>
+  </si>
+  <si>
+    <t>0.9068,0.0790,0.0017,0.0013</t>
+  </si>
+  <si>
+    <t>0.6385,0.4054,0.0095,0.0019</t>
+  </si>
+  <si>
+    <t>0.8537,0.1582,0.0016,0.0010</t>
+  </si>
+  <si>
+    <t>0.9708,0.0142,0.0003,0.0010</t>
+  </si>
+  <si>
+    <t>0.8735,0.1654,0.0018,0.0006</t>
+  </si>
+  <si>
+    <t>0.9290,0.0333,0.0013,0.0022</t>
+  </si>
+  <si>
+    <t>0.7256,0.3121,0.0018,0.0010</t>
+  </si>
+  <si>
+    <t>0.3258,0.0155,0.7598,0.0011</t>
+  </si>
+  <si>
+    <t>0.6499,0.0408,0.3574,0.0037</t>
+  </si>
+  <si>
+    <t>0.9834,0.0033,0.0070,0.0004</t>
+  </si>
+  <si>
+    <t>0.9085,0.0066,0.1520,0.0009</t>
+  </si>
+  <si>
+    <t>0.2389,0.8234,0.0093,0.0011</t>
+  </si>
+  <si>
+    <t>0.5460,0.5751,0.0071,0.0009</t>
+  </si>
+  <si>
+    <t>0.5120,0.6669,0.0062,0.0005</t>
+  </si>
+  <si>
+    <t>0.3708,0.7380,0.0071,0.0010</t>
+  </si>
+  <si>
+    <t>0.1587,0.9147,0.0028,0.0005</t>
+  </si>
+  <si>
+    <t>0.4521,0.6928,0.0083,0.0006</t>
+  </si>
+  <si>
+    <t>0.6135,0.5568,0.0042,0.0004</t>
+  </si>
+  <si>
+    <t>0.9450,0.0369,0.0110,0.0007</t>
+  </si>
+  <si>
+    <t>0.8488,0.0174,0.2068,0.0019</t>
+  </si>
+  <si>
+    <t>0.9342,0.0297,0.0208,0.0006</t>
+  </si>
+  <si>
+    <t>0.9160,0.0581,0.0101,0.0012</t>
+  </si>
+  <si>
+    <t>0.9158,0.0662,0.0184,0.0015</t>
+  </si>
+  <si>
+    <t>0.9430,0.0541,0.0052,0.0002</t>
+  </si>
+  <si>
+    <t>0.9715,0.0183,0.0027,0.0001</t>
+  </si>
+  <si>
+    <t>0.8564,0.1352,0.0155,0.0011</t>
+  </si>
+  <si>
+    <t>0.5580,0.1433,0.0701,0.0004</t>
+  </si>
+  <si>
+    <t>0.6628,0.4402,0.0120,0.0003</t>
+  </si>
+  <si>
+    <t>0.7918,0.2978,0.0049,0.0004</t>
+  </si>
+  <si>
+    <t>0.2538,0.8332,0.0121,0.0007</t>
+  </si>
+  <si>
+    <t>0.9089,0.1284,0.0032,0.0002</t>
+  </si>
+  <si>
+    <t>0.7232,0.2374,0.0053,0.0047</t>
+  </si>
+  <si>
+    <t>0.8007,0.2932,0.0033,0.0003</t>
+  </si>
+  <si>
+    <t>0.6457,0.3959,0.0062,0.0018</t>
+  </si>
+  <si>
+    <t>0.7674,0.3236,0.0050,0.0006</t>
+  </si>
+  <si>
+    <t>0.8430,0.2174,0.0052,0.0006</t>
+  </si>
+  <si>
+    <t>0.7742,0.3128,0.0040,0.0008</t>
+  </si>
+  <si>
+    <t>0.7934,0.2148,0.0209,0.0039</t>
+  </si>
+  <si>
+    <t>0.9350,0.0132,0.0947,0.0008</t>
+  </si>
+  <si>
+    <t>0.8630,0.0246,0.1338,0.0005</t>
+  </si>
+  <si>
+    <t>0.7968,0.0063,0.4143,0.0009</t>
+  </si>
+  <si>
+    <t>0.8016,0.0106,0.3240,0.0015</t>
+  </si>
+  <si>
+    <t>0.9445,0.0448,0.0066,0.0004</t>
+  </si>
+  <si>
+    <t>0.9187,0.0251,0.0419,0.0030</t>
+  </si>
+  <si>
+    <t>0.9152,0.0302,0.0479,0.0015</t>
+  </si>
+  <si>
+    <t>0.9688,0.0163,0.0054,0.0005</t>
+  </si>
+  <si>
+    <t>0.7663,0.1897,0.0121,0.0049</t>
+  </si>
+  <si>
+    <t>0.8738,0.0378,0.0170,0.0309</t>
+  </si>
+  <si>
+    <t>0.9218,0.0138,0.0190,0.0208</t>
+  </si>
+  <si>
+    <t>0.9182,0.0201,0.0221,0.0072</t>
+  </si>
+  <si>
+    <t>0.2692,0.4728,0.2623,0.0026</t>
+  </si>
+  <si>
+    <t>0.8890,0.1371,0.0042,0.0007</t>
+  </si>
+  <si>
+    <t>0.9609,0.0301,0.0028,0.0005</t>
+  </si>
+  <si>
+    <t>0.5887,0.4783,0.0173,0.0029</t>
+  </si>
+  <si>
+    <t>0.7141,0.3592,0.0050,0.0008</t>
+  </si>
+  <si>
+    <t>0.9158,0.0789,0.0055,0.0018</t>
+  </si>
+  <si>
+    <t>0.8666,0.1084,0.0197,0.0027</t>
+  </si>
+  <si>
+    <t>0.7899,0.2238,0.0023,0.0012</t>
+  </si>
+  <si>
+    <t>0.6386,0.0546,0.4493,0.0235</t>
+  </si>
+  <si>
+    <t>0.9761,0.0090,0.0010,0.0010</t>
+  </si>
+  <si>
+    <t>0.8823,0.1201,0.0060,0.0017</t>
+  </si>
+  <si>
+    <t>0.8411,0.1916,0.0050,0.0005</t>
+  </si>
+  <si>
+    <t>0.9428,0.0580,0.0022,0.0003</t>
+  </si>
+  <si>
+    <t>0.8115,0.1944,0.0036,0.0007</t>
+  </si>
+  <si>
+    <t>0.8511,0.1547,0.0131,0.0009</t>
+  </si>
+  <si>
+    <t>0.8268,0.1795,0.0122,0.0006</t>
+  </si>
+  <si>
+    <t>0.9235,0.0675,0.0074,0.0004</t>
+  </si>
+  <si>
+    <t>0.8217,0.1446,0.0071,0.0038</t>
+  </si>
+  <si>
+    <t>0.7377,0.3039,0.0097,0.0050</t>
+  </si>
+  <si>
+    <t>0.8764,0.1415,0.0028,0.0009</t>
+  </si>
+  <si>
+    <t>0.8543,0.1525,0.0023,0.0011</t>
+  </si>
+  <si>
+    <t>0.8091,0.2363,0.0038,0.0008</t>
+  </si>
+  <si>
+    <t>0.5630,0.5247,0.0101,0.0023</t>
+  </si>
+  <si>
+    <t>0.9255,0.0698,0.0032,0.0008</t>
+  </si>
+  <si>
+    <t>0.8769,0.1176,0.0046,0.0021</t>
+  </si>
+  <si>
+    <t>0.7433,0.3566,0.0052,0.0006</t>
+  </si>
+  <si>
+    <t>0.4479,0.6419,0.0136,0.0010</t>
+  </si>
+  <si>
+    <t>0.7083,0.3974,0.0032,0.0004</t>
+  </si>
+  <si>
+    <t>0.2481,0.5942,0.2414,0.0028</t>
+  </si>
+  <si>
+    <t>0.8545,0.1967,0.0033,0.0006</t>
+  </si>
+  <si>
+    <t>0.9428,0.0652,0.0013,0.0006</t>
+  </si>
+  <si>
+    <t>0.9125,0.1274,0.0012,0.0004</t>
+  </si>
+  <si>
+    <t>0.4716,0.6153,0.0195,0.0022</t>
+  </si>
+  <si>
+    <t>0.1567,0.2650,0.6935,0.0021</t>
+  </si>
+  <si>
+    <t>0.9516,0.0421,0.0029,0.0012</t>
+  </si>
+  <si>
+    <t>0.4321,0.0026,0.7515,0.0010</t>
+  </si>
+  <si>
+    <t>0.9418,0.0028,0.0838,0.0006</t>
+  </si>
+  <si>
+    <t>0.9051,0.0364,0.0531,0.0026</t>
+  </si>
+  <si>
+    <t>0.4442,0.0136,0.7017,0.0015</t>
+  </si>
+  <si>
+    <t>0.8978,0.0026,0.2340,0.0008</t>
+  </si>
+  <si>
+    <t>0.6755,0.0197,0.4099,0.0019</t>
+  </si>
+  <si>
+    <t>0.9250,0.0224,0.0519,0.0011</t>
+  </si>
+  <si>
+    <t>0.9206,0.0281,0.0419,0.0011</t>
+  </si>
+  <si>
+    <t>0.9625,0.0258,0.0043,0.0003</t>
+  </si>
+  <si>
+    <t>0.7190,0.2451,0.0252,0.0004</t>
+  </si>
+  <si>
+    <t>0.9255,0.0415,0.0183,0.0004</t>
+  </si>
+  <si>
+    <t>0.8297,0.0969,0.0348,0.0005</t>
+  </si>
+  <si>
+    <t>0.8932,0.0541,0.0314,0.0030</t>
+  </si>
+  <si>
+    <t>0.5396,0.4775,0.0268,0.0034</t>
+  </si>
+  <si>
+    <t>0.9073,0.0357,0.0513,0.0008</t>
+  </si>
+  <si>
+    <t>0.5211,0.5624,0.0115,0.0023</t>
+  </si>
+  <si>
+    <t>0.2319,0.8599,0.0033,0.0006</t>
+  </si>
+  <si>
+    <t>0.3684,0.7618,0.0073,0.0007</t>
+  </si>
+  <si>
+    <t>0.3664,0.7589,0.0087,0.0009</t>
+  </si>
+  <si>
+    <t>0.9299,0.0561,0.0012,0.0013</t>
+  </si>
+  <si>
+    <t>0.9767,0.0090,0.0081,0.0002</t>
+  </si>
+  <si>
+    <t>0.8186,0.1589,0.0255,0.0006</t>
+  </si>
+  <si>
+    <t>0.9542,0.0217,0.0117,0.0005</t>
+  </si>
+  <si>
+    <t>0.9126,0.0393,0.0305,0.0013</t>
+  </si>
+  <si>
+    <t>0.8630,0.0971,0.0294,0.0024</t>
+  </si>
+  <si>
+    <t>0.7885,0.0332,0.2036,0.0011</t>
+  </si>
+  <si>
+    <t>0.9477,0.0087,0.0516,0.0007</t>
+  </si>
+  <si>
+    <t>0.9848,0.0017,0.0177,0.0003</t>
+  </si>
+  <si>
+    <t>0.9443,0.0024,0.0989,0.0005</t>
+  </si>
+  <si>
+    <t>0.9490,0.0071,0.0450,0.0003</t>
+  </si>
+  <si>
+    <t>0.9583,0.0241,0.0005,0.0011</t>
+  </si>
+  <si>
+    <t>0.9594,0.0278,0.0009,0.0011</t>
+  </si>
+  <si>
+    <t>0.8884,0.1391,0.0016,0.0004</t>
+  </si>
+  <si>
+    <t>0.6697,0.4430,0.0070,0.0011</t>
+  </si>
+  <si>
+    <t>0.7907,0.2632,0.0040,0.0013</t>
+  </si>
+  <si>
+    <t>0.7267,0.3486,0.0111,0.0013</t>
+  </si>
+  <si>
+    <t>0.8341,0.1890,0.0031,0.0012</t>
+  </si>
+  <si>
+    <t>0.5488,0.5466,0.0139,0.0014</t>
+  </si>
+  <si>
+    <t>0.8922,0.1024,0.0220,0.0007</t>
+  </si>
+  <si>
+    <t>0.8847,0.1194,0.0096,0.0007</t>
+  </si>
+  <si>
+    <t>0.9276,0.0677,0.0024,0.0011</t>
+  </si>
+  <si>
+    <t>0.3609,0.0059,0.7890,0.0006</t>
+  </si>
+  <si>
+    <t>0.2981,0.0161,0.7640,0.0012</t>
+  </si>
+  <si>
+    <t>0.7865,0.0103,0.3051,0.0003</t>
+  </si>
+  <si>
+    <t>0.0484,0.0085,0.9742,0.0008</t>
+  </si>
+  <si>
+    <t>0.8594,0.0120,0.2164,0.0010</t>
+  </si>
+  <si>
+    <t>0.1804,0.0442,0.8144,0.0045</t>
+  </si>
+  <si>
+    <t>0.8280,0.0083,0.3140,0.0014</t>
+  </si>
+  <si>
+    <t>0.9337,0.0260,0.0235,0.0009</t>
+  </si>
+  <si>
+    <t>0.9772,0.0064,0.0083,0.0003</t>
+  </si>
+  <si>
+    <t>0.9330,0.0261,0.0330,0.0012</t>
+  </si>
+  <si>
+    <t>0.9524,0.0154,0.0168,0.0008</t>
+  </si>
+  <si>
+    <t>0.8025,0.2732,0.0030,0.0008</t>
+  </si>
+  <si>
+    <t>0.8570,0.1341,0.0017,0.0015</t>
+  </si>
+  <si>
+    <t>0.8395,0.1715,0.0015,0.0009</t>
+  </si>
+  <si>
+    <t>0.8167,0.2004,0.0036,0.0014</t>
+  </si>
+  <si>
+    <t>0.6748,0.4539,0.0015,0.0007</t>
+  </si>
+  <si>
+    <t>0.9417,0.0373,0.0009,0.0019</t>
+  </si>
+  <si>
+    <t>0.6563,0.5000,0.0067,0.0005</t>
+  </si>
+  <si>
+    <t>0.8143,0.1987,0.0030,0.0017</t>
+  </si>
+  <si>
+    <t>0.8819,0.0359,0.0877,0.0013</t>
+  </si>
+  <si>
+    <t>0.1680,0.1104,0.7498,0.0011</t>
+  </si>
+  <si>
+    <t>0.2847,0.0824,0.6337,0.0150</t>
+  </si>
+  <si>
+    <t>0.8725,0.0095,0.1810,0.0062</t>
+  </si>
+  <si>
+    <t>0.6273,0.0041,0.5590,0.0010</t>
+  </si>
+  <si>
+    <t>0.9677,0.0055,0.0218,0.0014</t>
+  </si>
+  <si>
+    <t>0.9159,0.0116,0.0968,0.0010</t>
+  </si>
+  <si>
+    <t>0.9830,0.0011,0.0195,0.0007</t>
+  </si>
+  <si>
+    <t>0.8539,0.0907,0.0321,0.0054</t>
+  </si>
+  <si>
+    <t>0.9478,0.0137,0.0136,0.0069</t>
+  </si>
+  <si>
+    <t>0.9332,0.0395,0.0035,0.0030</t>
+  </si>
+  <si>
+    <t>0.9439,0.0111,0.0040,0.0176</t>
+  </si>
+  <si>
+    <t>0.9406,0.0147,0.0184,0.0147</t>
+  </si>
+  <si>
+    <t>0.9469,0.0325,0.0078,0.0008</t>
   </si>
 </sst>
 </file>
@@ -2051,7 +2051,7 @@
         <v>259</v>
       </c>
       <c r="C9" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D9" t="s">
         <v>271</v>
@@ -2079,7 +2079,7 @@
         <v>259</v>
       </c>
       <c r="C11" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D11" t="s">
         <v>273</v>
@@ -2205,7 +2205,7 @@
         <v>262</v>
       </c>
       <c r="C20" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D20" t="s">
         <v>282</v>
@@ -2219,7 +2219,7 @@
         <v>262</v>
       </c>
       <c r="C21" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D21" t="s">
         <v>283</v>
@@ -2401,7 +2401,7 @@
         <v>263</v>
       </c>
       <c r="C34" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D34" t="s">
         <v>296</v>
@@ -2681,7 +2681,7 @@
         <v>261</v>
       </c>
       <c r="C54" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D54" t="s">
         <v>316</v>
@@ -2751,7 +2751,7 @@
         <v>261</v>
       </c>
       <c r="C59" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D59" t="s">
         <v>321</v>
@@ -2807,7 +2807,7 @@
         <v>262</v>
       </c>
       <c r="C63" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D63" t="s">
         <v>325</v>
@@ -2821,7 +2821,7 @@
         <v>261</v>
       </c>
       <c r="C64" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D64" t="s">
         <v>326</v>
@@ -2835,7 +2835,7 @@
         <v>261</v>
       </c>
       <c r="C65" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D65" t="s">
         <v>327</v>
@@ -2849,7 +2849,7 @@
         <v>263</v>
       </c>
       <c r="C66" t="s">
-        <v>263</v>
+        <v>259</v>
       </c>
       <c r="D66" t="s">
         <v>328</v>
@@ -2877,7 +2877,7 @@
         <v>262</v>
       </c>
       <c r="C68" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D68" t="s">
         <v>330</v>
@@ -2933,7 +2933,7 @@
         <v>261</v>
       </c>
       <c r="C72" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D72" t="s">
         <v>334</v>
@@ -2989,7 +2989,7 @@
         <v>262</v>
       </c>
       <c r="C76" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D76" t="s">
         <v>338</v>
@@ -3171,7 +3171,7 @@
         <v>259</v>
       </c>
       <c r="C89" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D89" t="s">
         <v>351</v>
@@ -3241,7 +3241,7 @@
         <v>259</v>
       </c>
       <c r="C94" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D94" t="s">
         <v>356</v>
@@ -3255,7 +3255,7 @@
         <v>259</v>
       </c>
       <c r="C95" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D95" t="s">
         <v>357</v>
@@ -3269,7 +3269,7 @@
         <v>259</v>
       </c>
       <c r="C96" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D96" t="s">
         <v>358</v>
@@ -3507,7 +3507,7 @@
         <v>262</v>
       </c>
       <c r="C113" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D113" t="s">
         <v>375</v>
@@ -3535,7 +3535,7 @@
         <v>262</v>
       </c>
       <c r="C115" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D115" t="s">
         <v>377</v>
@@ -3703,7 +3703,7 @@
         <v>259</v>
       </c>
       <c r="C127" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D127" t="s">
         <v>389</v>
@@ -3731,7 +3731,7 @@
         <v>259</v>
       </c>
       <c r="C129" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D129" t="s">
         <v>391</v>
@@ -3815,7 +3815,7 @@
         <v>259</v>
       </c>
       <c r="C135" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D135" t="s">
         <v>397</v>
@@ -4305,7 +4305,7 @@
         <v>259</v>
       </c>
       <c r="C170" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D170" t="s">
         <v>432</v>
@@ -4361,7 +4361,7 @@
         <v>259</v>
       </c>
       <c r="C174" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D174" t="s">
         <v>436</v>
@@ -4389,7 +4389,7 @@
         <v>261</v>
       </c>
       <c r="C176" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D176" t="s">
         <v>438</v>
@@ -4417,7 +4417,7 @@
         <v>259</v>
       </c>
       <c r="C178" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D178" t="s">
         <v>440</v>
@@ -4445,7 +4445,7 @@
         <v>259</v>
       </c>
       <c r="C180" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D180" t="s">
         <v>442</v>
@@ -4459,7 +4459,7 @@
         <v>261</v>
       </c>
       <c r="C181" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D181" t="s">
         <v>443</v>
@@ -4543,7 +4543,7 @@
         <v>261</v>
       </c>
       <c r="C187" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D187" t="s">
         <v>449</v>
@@ -4599,7 +4599,7 @@
         <v>259</v>
       </c>
       <c r="C191" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D191" t="s">
         <v>453</v>
@@ -4697,7 +4697,7 @@
         <v>259</v>
       </c>
       <c r="C198" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D198" t="s">
         <v>460</v>
@@ -4739,7 +4739,7 @@
         <v>259</v>
       </c>
       <c r="C201" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D201" t="s">
         <v>463</v>
@@ -4837,7 +4837,7 @@
         <v>261</v>
       </c>
       <c r="C208" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D208" t="s">
         <v>470</v>
@@ -4921,7 +4921,7 @@
         <v>259</v>
       </c>
       <c r="C214" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D214" t="s">
         <v>476</v>
@@ -5005,7 +5005,7 @@
         <v>259</v>
       </c>
       <c r="C220" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D220" t="s">
         <v>482</v>
@@ -5061,7 +5061,7 @@
         <v>261</v>
       </c>
       <c r="C224" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D224" t="s">
         <v>486</v>
@@ -5215,7 +5215,7 @@
         <v>259</v>
       </c>
       <c r="C235" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D235" t="s">
         <v>497</v>
@@ -5299,7 +5299,7 @@
         <v>259</v>
       </c>
       <c r="C241" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D241" t="s">
         <v>503</v>
@@ -5355,7 +5355,7 @@
         <v>261</v>
       </c>
       <c r="C245" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D245" t="s">
         <v>507</v>

--- a/dataset_agreed/saved_models/hyperparameter_optimized_runs/pointcloud_HPO_run_2/epoch_40/per_file_predictions_epoch_40.xlsx
+++ b/dataset_agreed/saved_models/hyperparameter_optimized_runs/pointcloud_HPO_run_2/epoch_40/per_file_predictions_epoch_40.xlsx
@@ -808,769 +808,769 @@
     <t>0,1,1,0</t>
   </si>
   <si>
-    <t>0.8804,0.0931,0.0165,0.0020</t>
-  </si>
-  <si>
-    <t>0.8088,0.0735,0.0184,0.0271</t>
-  </si>
-  <si>
-    <t>0.8901,0.0648,0.0109,0.0049</t>
-  </si>
-  <si>
-    <t>0.8994,0.0709,0.0025,0.0019</t>
-  </si>
-  <si>
-    <t>0.7394,0.3220,0.0075,0.0018</t>
-  </si>
-  <si>
-    <t>0.7916,0.1884,0.0016,0.0015</t>
-  </si>
-  <si>
-    <t>0.8543,0.1778,0.0031,0.0011</t>
-  </si>
-  <si>
-    <t>0.4748,0.6612,0.0105,0.0013</t>
-  </si>
-  <si>
-    <t>0.8928,0.1235,0.0008,0.0005</t>
-  </si>
-  <si>
-    <t>0.8960,0.1476,0.0010,0.0004</t>
-  </si>
-  <si>
-    <t>0.9224,0.0787,0.0012,0.0013</t>
-  </si>
-  <si>
-    <t>0.5751,0.5712,0.0068,0.0009</t>
-  </si>
-  <si>
-    <t>0.8836,0.1153,0.0138,0.0003</t>
-  </si>
-  <si>
-    <t>0.9619,0.0143,0.0179,0.0005</t>
-  </si>
-  <si>
-    <t>0.8557,0.0420,0.1120,0.0018</t>
-  </si>
-  <si>
-    <t>0.8933,0.0461,0.0609,0.0026</t>
-  </si>
-  <si>
-    <t>0.9341,0.0401,0.0095,0.0007</t>
-  </si>
-  <si>
-    <t>0.3116,0.8463,0.0013,0.0000</t>
-  </si>
-  <si>
-    <t>0.2021,0.8744,0.0037,0.0006</t>
-  </si>
-  <si>
-    <t>0.7550,0.3006,0.0128,0.0011</t>
-  </si>
-  <si>
-    <t>0.3355,0.8339,0.0021,0.0002</t>
-  </si>
-  <si>
-    <t>0.5902,0.6109,0.0024,0.0001</t>
-  </si>
-  <si>
-    <t>0.9815,0.0031,0.0109,0.0004</t>
-  </si>
-  <si>
-    <t>0.9911,0.0007,0.0127,0.0001</t>
-  </si>
-  <si>
-    <t>0.9742,0.0034,0.0201,0.0003</t>
-  </si>
-  <si>
-    <t>0.9597,0.0068,0.0388,0.0003</t>
-  </si>
-  <si>
-    <t>0.9436,0.0221,0.0245,0.0009</t>
-  </si>
-  <si>
-    <t>0.8590,0.0266,0.1701,0.0022</t>
-  </si>
-  <si>
-    <t>0.2716,0.0146,0.8012,0.0034</t>
-  </si>
-  <si>
-    <t>0.9333,0.0834,0.0045,0.0003</t>
-  </si>
-  <si>
-    <t>0.9265,0.0548,0.0136,0.0009</t>
-  </si>
-  <si>
-    <t>0.0073,0.2470,0.9820,0.0110</t>
-  </si>
-  <si>
-    <t>0.3059,0.7344,0.0104,0.0001</t>
-  </si>
-  <si>
-    <t>0.7850,0.2143,0.0141,0.0028</t>
-  </si>
-  <si>
-    <t>0.6912,0.3333,0.0269,0.0027</t>
-  </si>
-  <si>
-    <t>0.8158,0.2656,0.0063,0.0006</t>
-  </si>
-  <si>
-    <t>0.9814,0.0163,0.0021,0.0001</t>
-  </si>
-  <si>
-    <t>0.8735,0.0494,0.0193,0.0002</t>
-  </si>
-  <si>
-    <t>0.9738,0.0021,0.0362,0.0004</t>
-  </si>
-  <si>
-    <t>0.9819,0.0017,0.0253,0.0003</t>
-  </si>
-  <si>
-    <t>0.9916,0.0012,0.0053,0.0001</t>
-  </si>
-  <si>
-    <t>0.8873,0.0021,0.2742,0.0005</t>
-  </si>
-  <si>
-    <t>0.7176,0.1257,0.0263,0.0002</t>
-  </si>
-  <si>
-    <t>0.9604,0.0028,0.0559,0.0002</t>
-  </si>
-  <si>
-    <t>0.8885,0.0900,0.0238,0.0011</t>
-  </si>
-  <si>
-    <t>0.9323,0.0597,0.0038,0.0002</t>
-  </si>
-  <si>
-    <t>0.8387,0.1493,0.0159,0.0005</t>
-  </si>
-  <si>
-    <t>0.9553,0.0309,0.0063,0.0001</t>
-  </si>
-  <si>
-    <t>0.2409,0.1122,0.6340,0.0021</t>
-  </si>
-  <si>
-    <t>0.2542,0.0552,0.7666,0.0015</t>
-  </si>
-  <si>
-    <t>0.9383,0.0043,0.1068,0.0017</t>
-  </si>
-  <si>
-    <t>0.7122,0.0090,0.4832,0.0018</t>
-  </si>
-  <si>
-    <t>0.8647,0.0044,0.2057,0.0003</t>
-  </si>
-  <si>
-    <t>0.6366,0.0140,0.3477,0.0004</t>
-  </si>
-  <si>
-    <t>0.8635,0.1179,0.0033,0.0020</t>
-  </si>
-  <si>
-    <t>0.9072,0.0845,0.0035,0.0015</t>
-  </si>
-  <si>
-    <t>0.8707,0.1313,0.0026,0.0012</t>
-  </si>
-  <si>
-    <t>0.6129,0.4749,0.0195,0.0011</t>
-  </si>
-  <si>
-    <t>0.8474,0.1189,0.0035,0.0030</t>
-  </si>
-  <si>
-    <t>0.7621,0.2363,0.0023,0.0017</t>
-  </si>
-  <si>
-    <t>0.9207,0.0789,0.0035,0.0011</t>
-  </si>
-  <si>
-    <t>0.5113,0.1439,0.4391,0.0028</t>
-  </si>
-  <si>
-    <t>0.3176,0.0217,0.8173,0.0011</t>
-  </si>
-  <si>
-    <t>0.6108,0.0127,0.5695,0.0030</t>
-  </si>
-  <si>
-    <t>0.6146,0.0763,0.1890,0.0005</t>
-  </si>
-  <si>
-    <t>0.2249,0.0141,0.8866,0.0006</t>
-  </si>
-  <si>
-    <t>0.6720,0.4471,0.0094,0.0002</t>
-  </si>
-  <si>
-    <t>0.4448,0.6816,0.0049,0.0001</t>
-  </si>
-  <si>
-    <t>0.9495,0.0366,0.0033,0.0012</t>
-  </si>
-  <si>
-    <t>0.9013,0.0950,0.0121,0.0006</t>
-  </si>
-  <si>
-    <t>0.1466,0.4336,0.2991,0.0044</t>
-  </si>
-  <si>
-    <t>0.8036,0.0109,0.3073,0.0007</t>
-  </si>
-  <si>
-    <t>0.9366,0.0047,0.1303,0.0005</t>
-  </si>
-  <si>
-    <t>0.0398,0.9503,0.0883,0.0005</t>
-  </si>
-  <si>
-    <t>0.0639,0.8993,0.0474,0.0001</t>
-  </si>
-  <si>
-    <t>0.8789,0.0527,0.0355,0.0111</t>
-  </si>
-  <si>
-    <t>0.9312,0.0200,0.0047,0.0110</t>
-  </si>
-  <si>
-    <t>0.9769,0.0067,0.0016,0.0024</t>
-  </si>
-  <si>
-    <t>0.9171,0.0375,0.0094,0.0089</t>
-  </si>
-  <si>
-    <t>0.9286,0.0203,0.0104,0.0145</t>
-  </si>
-  <si>
-    <t>0.9421,0.0123,0.0140,0.0092</t>
-  </si>
-  <si>
-    <t>0.7365,0.1989,0.0391,0.0007</t>
-  </si>
-  <si>
-    <t>0.5851,0.0079,0.5865,0.0022</t>
-  </si>
-  <si>
-    <t>0.7802,0.0302,0.3014,0.0019</t>
-  </si>
-  <si>
-    <t>0.8081,0.0295,0.1865,0.0009</t>
-  </si>
-  <si>
-    <t>0.7680,0.0691,0.1141,0.0014</t>
-  </si>
-  <si>
-    <t>0.4833,0.2292,0.0328,0.0001</t>
-  </si>
-  <si>
-    <t>0.4047,0.6621,0.0091,0.0022</t>
-  </si>
-  <si>
-    <t>0.9072,0.1088,0.0014,0.0004</t>
-  </si>
-  <si>
-    <t>0.6547,0.4343,0.0085,0.0014</t>
-  </si>
-  <si>
-    <t>0.8665,0.1013,0.0009,0.0017</t>
-  </si>
-  <si>
-    <t>0.7465,0.4035,0.0012,0.0004</t>
-  </si>
-  <si>
-    <t>0.5724,0.5479,0.0066,0.0010</t>
-  </si>
-  <si>
-    <t>0.9025,0.0884,0.0038,0.0019</t>
-  </si>
-  <si>
-    <t>0.7203,0.3770,0.0069,0.0013</t>
-  </si>
-  <si>
-    <t>0.6080,0.4077,0.0090,0.0044</t>
-  </si>
-  <si>
-    <t>0.9068,0.0790,0.0017,0.0013</t>
-  </si>
-  <si>
-    <t>0.6385,0.4054,0.0095,0.0019</t>
-  </si>
-  <si>
-    <t>0.8537,0.1582,0.0016,0.0010</t>
-  </si>
-  <si>
-    <t>0.9708,0.0142,0.0003,0.0010</t>
-  </si>
-  <si>
-    <t>0.8735,0.1654,0.0018,0.0006</t>
-  </si>
-  <si>
-    <t>0.9290,0.0333,0.0013,0.0022</t>
-  </si>
-  <si>
-    <t>0.7256,0.3121,0.0018,0.0010</t>
-  </si>
-  <si>
-    <t>0.3258,0.0155,0.7598,0.0011</t>
-  </si>
-  <si>
-    <t>0.6499,0.0408,0.3574,0.0037</t>
-  </si>
-  <si>
-    <t>0.9834,0.0033,0.0070,0.0004</t>
-  </si>
-  <si>
-    <t>0.9085,0.0066,0.1520,0.0009</t>
-  </si>
-  <si>
-    <t>0.2389,0.8234,0.0093,0.0011</t>
-  </si>
-  <si>
-    <t>0.5460,0.5751,0.0071,0.0009</t>
-  </si>
-  <si>
-    <t>0.5120,0.6669,0.0062,0.0005</t>
-  </si>
-  <si>
-    <t>0.3708,0.7380,0.0071,0.0010</t>
-  </si>
-  <si>
-    <t>0.1587,0.9147,0.0028,0.0005</t>
-  </si>
-  <si>
-    <t>0.4521,0.6928,0.0083,0.0006</t>
-  </si>
-  <si>
-    <t>0.6135,0.5568,0.0042,0.0004</t>
-  </si>
-  <si>
-    <t>0.9450,0.0369,0.0110,0.0007</t>
-  </si>
-  <si>
-    <t>0.8488,0.0174,0.2068,0.0019</t>
-  </si>
-  <si>
-    <t>0.9342,0.0297,0.0208,0.0006</t>
-  </si>
-  <si>
-    <t>0.9160,0.0581,0.0101,0.0012</t>
-  </si>
-  <si>
-    <t>0.9158,0.0662,0.0184,0.0015</t>
-  </si>
-  <si>
-    <t>0.9430,0.0541,0.0052,0.0002</t>
-  </si>
-  <si>
-    <t>0.9715,0.0183,0.0027,0.0001</t>
-  </si>
-  <si>
-    <t>0.8564,0.1352,0.0155,0.0011</t>
-  </si>
-  <si>
-    <t>0.5580,0.1433,0.0701,0.0004</t>
-  </si>
-  <si>
-    <t>0.6628,0.4402,0.0120,0.0003</t>
-  </si>
-  <si>
-    <t>0.7918,0.2978,0.0049,0.0004</t>
-  </si>
-  <si>
-    <t>0.2538,0.8332,0.0121,0.0007</t>
-  </si>
-  <si>
-    <t>0.9089,0.1284,0.0032,0.0002</t>
-  </si>
-  <si>
-    <t>0.7232,0.2374,0.0053,0.0047</t>
-  </si>
-  <si>
-    <t>0.8007,0.2932,0.0033,0.0003</t>
-  </si>
-  <si>
-    <t>0.6457,0.3959,0.0062,0.0018</t>
-  </si>
-  <si>
-    <t>0.7674,0.3236,0.0050,0.0006</t>
-  </si>
-  <si>
-    <t>0.8430,0.2174,0.0052,0.0006</t>
-  </si>
-  <si>
-    <t>0.7742,0.3128,0.0040,0.0008</t>
-  </si>
-  <si>
-    <t>0.7934,0.2148,0.0209,0.0039</t>
-  </si>
-  <si>
-    <t>0.9350,0.0132,0.0947,0.0008</t>
-  </si>
-  <si>
-    <t>0.8630,0.0246,0.1338,0.0005</t>
-  </si>
-  <si>
-    <t>0.7968,0.0063,0.4143,0.0009</t>
-  </si>
-  <si>
-    <t>0.8016,0.0106,0.3240,0.0015</t>
-  </si>
-  <si>
-    <t>0.9445,0.0448,0.0066,0.0004</t>
-  </si>
-  <si>
-    <t>0.9187,0.0251,0.0419,0.0030</t>
-  </si>
-  <si>
-    <t>0.9152,0.0302,0.0479,0.0015</t>
-  </si>
-  <si>
-    <t>0.9688,0.0163,0.0054,0.0005</t>
-  </si>
-  <si>
-    <t>0.7663,0.1897,0.0121,0.0049</t>
-  </si>
-  <si>
-    <t>0.8738,0.0378,0.0170,0.0309</t>
-  </si>
-  <si>
-    <t>0.9218,0.0138,0.0190,0.0208</t>
-  </si>
-  <si>
-    <t>0.9182,0.0201,0.0221,0.0072</t>
-  </si>
-  <si>
-    <t>0.2692,0.4728,0.2623,0.0026</t>
-  </si>
-  <si>
-    <t>0.8890,0.1371,0.0042,0.0007</t>
-  </si>
-  <si>
-    <t>0.9609,0.0301,0.0028,0.0005</t>
-  </si>
-  <si>
-    <t>0.5887,0.4783,0.0173,0.0029</t>
-  </si>
-  <si>
-    <t>0.7141,0.3592,0.0050,0.0008</t>
-  </si>
-  <si>
-    <t>0.9158,0.0789,0.0055,0.0018</t>
-  </si>
-  <si>
-    <t>0.8666,0.1084,0.0197,0.0027</t>
-  </si>
-  <si>
-    <t>0.7899,0.2238,0.0023,0.0012</t>
-  </si>
-  <si>
-    <t>0.6386,0.0546,0.4493,0.0235</t>
-  </si>
-  <si>
-    <t>0.9761,0.0090,0.0010,0.0010</t>
-  </si>
-  <si>
-    <t>0.8823,0.1201,0.0060,0.0017</t>
-  </si>
-  <si>
-    <t>0.8411,0.1916,0.0050,0.0005</t>
-  </si>
-  <si>
-    <t>0.9428,0.0580,0.0022,0.0003</t>
-  </si>
-  <si>
-    <t>0.8115,0.1944,0.0036,0.0007</t>
-  </si>
-  <si>
-    <t>0.8511,0.1547,0.0131,0.0009</t>
-  </si>
-  <si>
-    <t>0.8268,0.1795,0.0122,0.0006</t>
-  </si>
-  <si>
-    <t>0.9235,0.0675,0.0074,0.0004</t>
-  </si>
-  <si>
-    <t>0.8217,0.1446,0.0071,0.0038</t>
-  </si>
-  <si>
-    <t>0.7377,0.3039,0.0097,0.0050</t>
-  </si>
-  <si>
-    <t>0.8764,0.1415,0.0028,0.0009</t>
-  </si>
-  <si>
-    <t>0.8543,0.1525,0.0023,0.0011</t>
-  </si>
-  <si>
-    <t>0.8091,0.2363,0.0038,0.0008</t>
-  </si>
-  <si>
-    <t>0.5630,0.5247,0.0101,0.0023</t>
-  </si>
-  <si>
-    <t>0.9255,0.0698,0.0032,0.0008</t>
-  </si>
-  <si>
-    <t>0.8769,0.1176,0.0046,0.0021</t>
-  </si>
-  <si>
-    <t>0.7433,0.3566,0.0052,0.0006</t>
-  </si>
-  <si>
-    <t>0.4479,0.6419,0.0136,0.0010</t>
-  </si>
-  <si>
-    <t>0.7083,0.3974,0.0032,0.0004</t>
-  </si>
-  <si>
-    <t>0.2481,0.5942,0.2414,0.0028</t>
-  </si>
-  <si>
-    <t>0.8545,0.1967,0.0033,0.0006</t>
-  </si>
-  <si>
-    <t>0.9428,0.0652,0.0013,0.0006</t>
-  </si>
-  <si>
-    <t>0.9125,0.1274,0.0012,0.0004</t>
-  </si>
-  <si>
-    <t>0.4716,0.6153,0.0195,0.0022</t>
-  </si>
-  <si>
-    <t>0.1567,0.2650,0.6935,0.0021</t>
-  </si>
-  <si>
-    <t>0.9516,0.0421,0.0029,0.0012</t>
-  </si>
-  <si>
-    <t>0.4321,0.0026,0.7515,0.0010</t>
-  </si>
-  <si>
-    <t>0.9418,0.0028,0.0838,0.0006</t>
-  </si>
-  <si>
-    <t>0.9051,0.0364,0.0531,0.0026</t>
-  </si>
-  <si>
-    <t>0.4442,0.0136,0.7017,0.0015</t>
-  </si>
-  <si>
-    <t>0.8978,0.0026,0.2340,0.0008</t>
-  </si>
-  <si>
-    <t>0.6755,0.0197,0.4099,0.0019</t>
-  </si>
-  <si>
-    <t>0.9250,0.0224,0.0519,0.0011</t>
-  </si>
-  <si>
-    <t>0.9206,0.0281,0.0419,0.0011</t>
-  </si>
-  <si>
-    <t>0.9625,0.0258,0.0043,0.0003</t>
-  </si>
-  <si>
-    <t>0.7190,0.2451,0.0252,0.0004</t>
-  </si>
-  <si>
-    <t>0.9255,0.0415,0.0183,0.0004</t>
-  </si>
-  <si>
-    <t>0.8297,0.0969,0.0348,0.0005</t>
-  </si>
-  <si>
-    <t>0.8932,0.0541,0.0314,0.0030</t>
-  </si>
-  <si>
-    <t>0.5396,0.4775,0.0268,0.0034</t>
-  </si>
-  <si>
-    <t>0.9073,0.0357,0.0513,0.0008</t>
-  </si>
-  <si>
-    <t>0.5211,0.5624,0.0115,0.0023</t>
-  </si>
-  <si>
-    <t>0.2319,0.8599,0.0033,0.0006</t>
-  </si>
-  <si>
-    <t>0.3684,0.7618,0.0073,0.0007</t>
-  </si>
-  <si>
-    <t>0.3664,0.7589,0.0087,0.0009</t>
-  </si>
-  <si>
-    <t>0.9299,0.0561,0.0012,0.0013</t>
-  </si>
-  <si>
-    <t>0.9767,0.0090,0.0081,0.0002</t>
-  </si>
-  <si>
-    <t>0.8186,0.1589,0.0255,0.0006</t>
-  </si>
-  <si>
-    <t>0.9542,0.0217,0.0117,0.0005</t>
-  </si>
-  <si>
-    <t>0.9126,0.0393,0.0305,0.0013</t>
-  </si>
-  <si>
-    <t>0.8630,0.0971,0.0294,0.0024</t>
-  </si>
-  <si>
-    <t>0.7885,0.0332,0.2036,0.0011</t>
-  </si>
-  <si>
-    <t>0.9477,0.0087,0.0516,0.0007</t>
-  </si>
-  <si>
-    <t>0.9848,0.0017,0.0177,0.0003</t>
-  </si>
-  <si>
-    <t>0.9443,0.0024,0.0989,0.0005</t>
-  </si>
-  <si>
-    <t>0.9490,0.0071,0.0450,0.0003</t>
-  </si>
-  <si>
-    <t>0.9583,0.0241,0.0005,0.0011</t>
-  </si>
-  <si>
-    <t>0.9594,0.0278,0.0009,0.0011</t>
-  </si>
-  <si>
-    <t>0.8884,0.1391,0.0016,0.0004</t>
-  </si>
-  <si>
-    <t>0.6697,0.4430,0.0070,0.0011</t>
-  </si>
-  <si>
-    <t>0.7907,0.2632,0.0040,0.0013</t>
-  </si>
-  <si>
-    <t>0.7267,0.3486,0.0111,0.0013</t>
-  </si>
-  <si>
-    <t>0.8341,0.1890,0.0031,0.0012</t>
-  </si>
-  <si>
-    <t>0.5488,0.5466,0.0139,0.0014</t>
-  </si>
-  <si>
-    <t>0.8922,0.1024,0.0220,0.0007</t>
-  </si>
-  <si>
-    <t>0.8847,0.1194,0.0096,0.0007</t>
-  </si>
-  <si>
-    <t>0.9276,0.0677,0.0024,0.0011</t>
-  </si>
-  <si>
-    <t>0.3609,0.0059,0.7890,0.0006</t>
-  </si>
-  <si>
-    <t>0.2981,0.0161,0.7640,0.0012</t>
-  </si>
-  <si>
-    <t>0.7865,0.0103,0.3051,0.0003</t>
-  </si>
-  <si>
-    <t>0.0484,0.0085,0.9742,0.0008</t>
-  </si>
-  <si>
-    <t>0.8594,0.0120,0.2164,0.0010</t>
-  </si>
-  <si>
-    <t>0.1804,0.0442,0.8144,0.0045</t>
-  </si>
-  <si>
-    <t>0.8280,0.0083,0.3140,0.0014</t>
-  </si>
-  <si>
-    <t>0.9337,0.0260,0.0235,0.0009</t>
-  </si>
-  <si>
-    <t>0.9772,0.0064,0.0083,0.0003</t>
-  </si>
-  <si>
-    <t>0.9330,0.0261,0.0330,0.0012</t>
-  </si>
-  <si>
-    <t>0.9524,0.0154,0.0168,0.0008</t>
-  </si>
-  <si>
-    <t>0.8025,0.2732,0.0030,0.0008</t>
-  </si>
-  <si>
-    <t>0.8570,0.1341,0.0017,0.0015</t>
-  </si>
-  <si>
-    <t>0.8395,0.1715,0.0015,0.0009</t>
-  </si>
-  <si>
-    <t>0.8167,0.2004,0.0036,0.0014</t>
-  </si>
-  <si>
-    <t>0.6748,0.4539,0.0015,0.0007</t>
-  </si>
-  <si>
-    <t>0.9417,0.0373,0.0009,0.0019</t>
-  </si>
-  <si>
-    <t>0.6563,0.5000,0.0067,0.0005</t>
-  </si>
-  <si>
-    <t>0.8143,0.1987,0.0030,0.0017</t>
-  </si>
-  <si>
-    <t>0.8819,0.0359,0.0877,0.0013</t>
-  </si>
-  <si>
-    <t>0.1680,0.1104,0.7498,0.0011</t>
-  </si>
-  <si>
-    <t>0.2847,0.0824,0.6337,0.0150</t>
-  </si>
-  <si>
-    <t>0.8725,0.0095,0.1810,0.0062</t>
-  </si>
-  <si>
-    <t>0.6273,0.0041,0.5590,0.0010</t>
-  </si>
-  <si>
-    <t>0.9677,0.0055,0.0218,0.0014</t>
-  </si>
-  <si>
-    <t>0.9159,0.0116,0.0968,0.0010</t>
-  </si>
-  <si>
-    <t>0.9830,0.0011,0.0195,0.0007</t>
-  </si>
-  <si>
-    <t>0.8539,0.0907,0.0321,0.0054</t>
-  </si>
-  <si>
-    <t>0.9478,0.0137,0.0136,0.0069</t>
-  </si>
-  <si>
-    <t>0.9332,0.0395,0.0035,0.0030</t>
-  </si>
-  <si>
-    <t>0.9439,0.0111,0.0040,0.0176</t>
-  </si>
-  <si>
-    <t>0.9406,0.0147,0.0184,0.0147</t>
-  </si>
-  <si>
-    <t>0.9469,0.0325,0.0078,0.0008</t>
+    <t>0.8437,0.0128,0.0022,0.0874</t>
+  </si>
+  <si>
+    <t>0.0033,0.0023,0.0004,0.9980</t>
+  </si>
+  <si>
+    <t>0.7990,0.0279,0.0005,0.0560</t>
+  </si>
+  <si>
+    <t>0.1091,0.0025,0.0018,0.9625</t>
+  </si>
+  <si>
+    <t>0.9992,0.0000,0.0000,0.0004</t>
+  </si>
+  <si>
+    <t>0.9987,0.0002,0.0001,0.0003</t>
+  </si>
+  <si>
+    <t>0.9972,0.0004,0.0002,0.0014</t>
+  </si>
+  <si>
+    <t>0.9989,0.0001,0.0000,0.0005</t>
+  </si>
+  <si>
+    <t>0.9943,0.0025,0.0005,0.0008</t>
+  </si>
+  <si>
+    <t>0.9974,0.0004,0.0001,0.0009</t>
+  </si>
+  <si>
+    <t>0.9972,0.0010,0.0001,0.0003</t>
+  </si>
+  <si>
+    <t>0.9980,0.0005,0.0003,0.0003</t>
+  </si>
+  <si>
+    <t>0.9490,0.0065,0.0557,0.0005</t>
+  </si>
+  <si>
+    <t>0.1705,0.0026,0.9061,0.0024</t>
+  </si>
+  <si>
+    <t>0.0994,0.0035,0.9343,0.0011</t>
+  </si>
+  <si>
+    <t>0.0179,0.0223,0.9596,0.0176</t>
+  </si>
+  <si>
+    <t>0.9231,0.0102,0.0647,0.0084</t>
+  </si>
+  <si>
+    <t>0.0010,0.9978,0.0008,0.0001</t>
+  </si>
+  <si>
+    <t>0.0029,0.9942,0.0006,0.0019</t>
+  </si>
+  <si>
+    <t>0.0346,0.9559,0.0182,0.0026</t>
+  </si>
+  <si>
+    <t>0.0026,0.9952,0.0010,0.0010</t>
+  </si>
+  <si>
+    <t>0.0025,0.9938,0.0039,0.0013</t>
+  </si>
+  <si>
+    <t>0.7898,0.0091,0.3123,0.0089</t>
+  </si>
+  <si>
+    <t>0.7337,0.0067,0.3894,0.0049</t>
+  </si>
+  <si>
+    <t>0.0086,0.0007,0.9891,0.0017</t>
+  </si>
+  <si>
+    <t>0.2340,0.0047,0.8240,0.0050</t>
+  </si>
+  <si>
+    <t>0.0378,0.0094,0.9648,0.0045</t>
+  </si>
+  <si>
+    <t>0.1068,0.0070,0.8998,0.0080</t>
+  </si>
+  <si>
+    <t>0.0042,0.0008,0.9934,0.0011</t>
+  </si>
+  <si>
+    <t>0.0593,0.9510,0.0050,0.0085</t>
+  </si>
+  <si>
+    <t>0.5220,0.2563,0.3521,0.0177</t>
+  </si>
+  <si>
+    <t>0.0035,0.0071,0.9927,0.0063</t>
+  </si>
+  <si>
+    <t>0.0354,0.7718,0.2786,0.0008</t>
+  </si>
+  <si>
+    <t>0.8869,0.0644,0.0121,0.0250</t>
+  </si>
+  <si>
+    <t>0.7921,0.2303,0.0222,0.0033</t>
+  </si>
+  <si>
+    <t>0.2171,0.8555,0.0087,0.0013</t>
+  </si>
+  <si>
+    <t>0.0219,0.9708,0.0398,0.0017</t>
+  </si>
+  <si>
+    <t>0.0274,0.1202,0.6088,0.0833</t>
+  </si>
+  <si>
+    <t>0.1972,0.0022,0.8759,0.0043</t>
+  </si>
+  <si>
+    <t>0.2597,0.0074,0.8731,0.0021</t>
+  </si>
+  <si>
+    <t>0.1058,0.0005,0.8631,0.0099</t>
+  </si>
+  <si>
+    <t>0.0239,0.0674,0.9764,0.0007</t>
+  </si>
+  <si>
+    <t>0.0439,0.8854,0.0300,0.0017</t>
+  </si>
+  <si>
+    <t>0.0069,0.0059,0.9818,0.0131</t>
+  </si>
+  <si>
+    <t>0.5682,0.1391,0.0121,0.2776</t>
+  </si>
+  <si>
+    <t>0.0009,0.9935,0.0012,0.0172</t>
+  </si>
+  <si>
+    <t>0.0044,0.9740,0.0470,0.0084</t>
+  </si>
+  <si>
+    <t>0.0035,0.9884,0.0103,0.0041</t>
+  </si>
+  <si>
+    <t>0.0036,0.0117,0.9894,0.0090</t>
+  </si>
+  <si>
+    <t>0.0041,0.1414,0.9766,0.0043</t>
+  </si>
+  <si>
+    <t>0.1059,0.0225,0.8660,0.0289</t>
+  </si>
+  <si>
+    <t>0.0030,0.0016,0.9970,0.0002</t>
+  </si>
+  <si>
+    <t>0.0105,0.0036,0.9892,0.0013</t>
+  </si>
+  <si>
+    <t>0.0107,0.0092,0.9850,0.0022</t>
+  </si>
+  <si>
+    <t>0.9676,0.0310,0.0010,0.0022</t>
+  </si>
+  <si>
+    <t>0.9835,0.0082,0.0035,0.0016</t>
+  </si>
+  <si>
+    <t>0.9858,0.0050,0.0013,0.0027</t>
+  </si>
+  <si>
+    <t>0.0103,0.0362,0.9875,0.0023</t>
+  </si>
+  <si>
+    <t>0.9948,0.0013,0.0009,0.0012</t>
+  </si>
+  <si>
+    <t>0.9958,0.0024,0.0001,0.0003</t>
+  </si>
+  <si>
+    <t>0.9448,0.0575,0.0010,0.0035</t>
+  </si>
+  <si>
+    <t>0.0009,0.3627,0.9930,0.0019</t>
+  </si>
+  <si>
+    <t>0.0159,0.0353,0.9788,0.0069</t>
+  </si>
+  <si>
+    <t>0.0017,0.0014,0.9968,0.0015</t>
+  </si>
+  <si>
+    <t>0.0009,0.9423,0.9848,0.0005</t>
+  </si>
+  <si>
+    <t>0.0028,0.0043,0.9954,0.0020</t>
+  </si>
+  <si>
+    <t>0.0145,0.9757,0.0156,0.0018</t>
+  </si>
+  <si>
+    <t>0.0044,0.9924,0.0147,0.0001</t>
+  </si>
+  <si>
+    <t>0.8371,0.0219,0.2356,0.0035</t>
+  </si>
+  <si>
+    <t>0.0747,0.2409,0.8713,0.0059</t>
+  </si>
+  <si>
+    <t>0.0078,0.2182,0.9866,0.0039</t>
+  </si>
+  <si>
+    <t>0.0034,0.6872,0.9675,0.0015</t>
+  </si>
+  <si>
+    <t>0.0089,0.9165,0.4792,0.0007</t>
+  </si>
+  <si>
+    <t>0.0009,0.9878,0.5849,0.0004</t>
+  </si>
+  <si>
+    <t>0.0046,0.9752,0.5789,0.0008</t>
+  </si>
+  <si>
+    <t>0.0035,0.0007,0.0015,0.9970</t>
+  </si>
+  <si>
+    <t>0.0014,0.0011,0.0001,0.9993</t>
+  </si>
+  <si>
+    <t>0.0179,0.0009,0.0002,0.9954</t>
+  </si>
+  <si>
+    <t>0.0034,0.0037,0.0020,0.9969</t>
+  </si>
+  <si>
+    <t>0.0037,0.0008,0.0027,0.9969</t>
+  </si>
+  <si>
+    <t>0.0079,0.0025,0.0006,0.9962</t>
+  </si>
+  <si>
+    <t>0.0009,0.9853,0.8897,0.0005</t>
+  </si>
+  <si>
+    <t>0.0048,0.3262,0.9855,0.0010</t>
+  </si>
+  <si>
+    <t>0.0109,0.4193,0.9070,0.0050</t>
+  </si>
+  <si>
+    <t>0.0010,0.7628,0.9950,0.0005</t>
+  </si>
+  <si>
+    <t>0.0008,0.9379,0.9737,0.0002</t>
+  </si>
+  <si>
+    <t>0.0100,0.9413,0.1712,0.0018</t>
+  </si>
+  <si>
+    <t>0.9948,0.0016,0.0003,0.0013</t>
+  </si>
+  <si>
+    <t>0.9820,0.0107,0.0032,0.0028</t>
+  </si>
+  <si>
+    <t>0.9941,0.0023,0.0002,0.0007</t>
+  </si>
+  <si>
+    <t>0.9937,0.0015,0.0002,0.0017</t>
+  </si>
+  <si>
+    <t>0.9910,0.0039,0.0003,0.0012</t>
+  </si>
+  <si>
+    <t>0.9970,0.0007,0.0002,0.0007</t>
+  </si>
+  <si>
+    <t>0.9956,0.0011,0.0012,0.0008</t>
+  </si>
+  <si>
+    <t>0.9947,0.0033,0.0003,0.0006</t>
+  </si>
+  <si>
+    <t>0.9971,0.0004,0.0017,0.0005</t>
+  </si>
+  <si>
+    <t>0.9971,0.0009,0.0001,0.0004</t>
+  </si>
+  <si>
+    <t>0.9974,0.0005,0.0001,0.0006</t>
+  </si>
+  <si>
+    <t>0.9982,0.0003,0.0002,0.0005</t>
+  </si>
+  <si>
+    <t>0.9979,0.0006,0.0000,0.0003</t>
+  </si>
+  <si>
+    <t>0.9936,0.0055,0.0003,0.0003</t>
+  </si>
+  <si>
+    <t>0.9944,0.0012,0.0008,0.0017</t>
+  </si>
+  <si>
+    <t>0.9979,0.0002,0.0002,0.0011</t>
+  </si>
+  <si>
+    <t>0.0133,0.0124,0.9806,0.0061</t>
+  </si>
+  <si>
+    <t>0.0939,0.0019,0.9108,0.0093</t>
+  </si>
+  <si>
+    <t>0.9432,0.0093,0.0259,0.0065</t>
+  </si>
+  <si>
+    <t>0.0330,0.0036,0.9796,0.0009</t>
+  </si>
+  <si>
+    <t>0.0082,0.9921,0.0009,0.0002</t>
+  </si>
+  <si>
+    <t>0.0015,0.9967,0.0006,0.0002</t>
+  </si>
+  <si>
+    <t>0.0069,0.9886,0.0018,0.0018</t>
+  </si>
+  <si>
+    <t>0.0523,0.9530,0.0031,0.0084</t>
+  </si>
+  <si>
+    <t>0.0088,0.9870,0.0030,0.0008</t>
+  </si>
+  <si>
+    <t>0.0017,0.9956,0.0031,0.0008</t>
+  </si>
+  <si>
+    <t>0.0975,0.9210,0.0144,0.0031</t>
+  </si>
+  <si>
+    <t>0.3910,0.6030,0.0178,0.0291</t>
+  </si>
+  <si>
+    <t>0.0435,0.0032,0.9603,0.0028</t>
+  </si>
+  <si>
+    <t>0.5927,0.0249,0.4205,0.0279</t>
+  </si>
+  <si>
+    <t>0.5148,0.0243,0.5876,0.0130</t>
+  </si>
+  <si>
+    <t>0.0448,0.1487,0.0752,0.9052</t>
+  </si>
+  <si>
+    <t>0.0031,0.9906,0.0109,0.0010</t>
+  </si>
+  <si>
+    <t>0.0015,0.9930,0.0038,0.0049</t>
+  </si>
+  <si>
+    <t>0.0011,0.9955,0.0022,0.0019</t>
+  </si>
+  <si>
+    <t>0.0020,0.6751,0.9712,0.0010</t>
+  </si>
+  <si>
+    <t>0.0126,0.9851,0.0057,0.0003</t>
+  </si>
+  <si>
+    <t>0.5682,0.4981,0.0276,0.0032</t>
+  </si>
+  <si>
+    <t>0.6923,0.4357,0.0046,0.0021</t>
+  </si>
+  <si>
+    <t>0.9900,0.0074,0.0009,0.0007</t>
+  </si>
+  <si>
+    <t>0.9965,0.0004,0.0003,0.0013</t>
+  </si>
+  <si>
+    <t>0.9822,0.0069,0.0026,0.0033</t>
+  </si>
+  <si>
+    <t>0.9794,0.0067,0.0068,0.0028</t>
+  </si>
+  <si>
+    <t>0.9963,0.0003,0.0003,0.0019</t>
+  </si>
+  <si>
+    <t>0.9874,0.0027,0.0087,0.0023</t>
+  </si>
+  <si>
+    <t>0.9971,0.0005,0.0003,0.0006</t>
+  </si>
+  <si>
+    <t>0.9927,0.0035,0.0007,0.0010</t>
+  </si>
+  <si>
+    <t>0.0229,0.0970,0.9673,0.0035</t>
+  </si>
+  <si>
+    <t>0.0061,0.2712,0.9742,0.0033</t>
+  </si>
+  <si>
+    <t>0.0072,0.0214,0.9845,0.0025</t>
+  </si>
+  <si>
+    <t>0.0327,0.0282,0.9367,0.0059</t>
+  </si>
+  <si>
+    <t>0.9897,0.0007,0.0082,0.0007</t>
+  </si>
+  <si>
+    <t>0.9367,0.0116,0.0547,0.0052</t>
+  </si>
+  <si>
+    <t>0.1334,0.0043,0.8629,0.0151</t>
+  </si>
+  <si>
+    <t>0.8758,0.0558,0.0552,0.0046</t>
+  </si>
+  <si>
+    <t>0.3971,0.0009,0.0007,0.8579</t>
+  </si>
+  <si>
+    <t>0.0002,0.0002,0.0027,0.9991</t>
+  </si>
+  <si>
+    <t>0.0008,0.0038,0.0007,0.9990</t>
+  </si>
+  <si>
+    <t>0.0043,0.0001,0.0004,0.9982</t>
+  </si>
+  <si>
+    <t>0.0040,0.9272,0.8249,0.0024</t>
+  </si>
+  <si>
+    <t>0.9916,0.0024,0.0022,0.0012</t>
+  </si>
+  <si>
+    <t>0.2346,0.8080,0.0043,0.0129</t>
+  </si>
+  <si>
+    <t>0.9840,0.0043,0.0005,0.0057</t>
+  </si>
+  <si>
+    <t>0.1731,0.8315,0.0153,0.0070</t>
+  </si>
+  <si>
+    <t>0.9936,0.0004,0.0008,0.0019</t>
+  </si>
+  <si>
+    <t>0.6993,0.0064,0.0015,0.3645</t>
+  </si>
+  <si>
+    <t>0.9967,0.0005,0.0002,0.0008</t>
+  </si>
+  <si>
+    <t>0.0068,0.0315,0.9098,0.3021</t>
+  </si>
+  <si>
+    <t>0.9679,0.0006,0.0005,0.0503</t>
+  </si>
+  <si>
+    <t>0.9298,0.0035,0.0017,0.0660</t>
+  </si>
+  <si>
+    <t>0.0429,0.9203,0.0434,0.0192</t>
+  </si>
+  <si>
+    <t>0.9647,0.0070,0.0032,0.0091</t>
+  </si>
+  <si>
+    <t>0.9501,0.0694,0.0033,0.0010</t>
+  </si>
+  <si>
+    <t>0.2278,0.8022,0.0199,0.0122</t>
+  </si>
+  <si>
+    <t>0.5357,0.5302,0.0247,0.0079</t>
+  </si>
+  <si>
+    <t>0.9272,0.0558,0.0201,0.0050</t>
+  </si>
+  <si>
+    <t>0.9930,0.0035,0.0010,0.0010</t>
+  </si>
+  <si>
+    <t>0.9961,0.0007,0.0002,0.0013</t>
+  </si>
+  <si>
+    <t>0.9972,0.0006,0.0002,0.0008</t>
+  </si>
+  <si>
+    <t>0.9959,0.0003,0.0004,0.0022</t>
+  </si>
+  <si>
+    <t>0.9914,0.0019,0.0009,0.0029</t>
+  </si>
+  <si>
+    <t>0.9906,0.0054,0.0010,0.0012</t>
+  </si>
+  <si>
+    <t>0.9948,0.0006,0.0005,0.0026</t>
+  </si>
+  <si>
+    <t>0.9944,0.0004,0.0004,0.0029</t>
+  </si>
+  <si>
+    <t>0.6372,0.3357,0.0038,0.0140</t>
+  </si>
+  <si>
+    <t>0.2408,0.8396,0.0062,0.0008</t>
+  </si>
+  <si>
+    <t>0.3190,0.7996,0.0040,0.0018</t>
+  </si>
+  <si>
+    <t>0.5246,0.5194,0.0732,0.0155</t>
+  </si>
+  <si>
+    <t>0.9530,0.0499,0.0027,0.0027</t>
+  </si>
+  <si>
+    <t>0.9720,0.0179,0.0016,0.0028</t>
+  </si>
+  <si>
+    <t>0.9932,0.0034,0.0020,0.0006</t>
+  </si>
+  <si>
+    <t>0.7255,0.4088,0.0034,0.0036</t>
+  </si>
+  <si>
+    <t>0.0011,0.0126,0.9984,0.0005</t>
+  </si>
+  <si>
+    <t>0.9518,0.0351,0.0140,0.0032</t>
+  </si>
+  <si>
+    <t>0.0072,0.0009,0.9921,0.0005</t>
+  </si>
+  <si>
+    <t>0.0020,0.0766,0.9919,0.0019</t>
+  </si>
+  <si>
+    <t>0.2854,0.0220,0.7599,0.0188</t>
+  </si>
+  <si>
+    <t>0.0055,0.1690,0.9849,0.0032</t>
+  </si>
+  <si>
+    <t>0.0089,0.0125,0.9802,0.0078</t>
+  </si>
+  <si>
+    <t>0.0019,0.0007,0.9961,0.0017</t>
+  </si>
+  <si>
+    <t>0.0083,0.0135,0.9807,0.0091</t>
+  </si>
+  <si>
+    <t>0.5146,0.0447,0.4729,0.0284</t>
+  </si>
+  <si>
+    <t>0.1207,0.0353,0.8726,0.0062</t>
+  </si>
+  <si>
+    <t>0.1213,0.0138,0.9200,0.0013</t>
+  </si>
+  <si>
+    <t>0.2674,0.1873,0.4438,0.0100</t>
+  </si>
+  <si>
+    <t>0.1690,0.0628,0.7541,0.0059</t>
+  </si>
+  <si>
+    <t>0.5723,0.0727,0.2680,0.0021</t>
+  </si>
+  <si>
+    <t>0.4862,0.1094,0.4206,0.0072</t>
+  </si>
+  <si>
+    <t>0.2377,0.0526,0.7388,0.0156</t>
+  </si>
+  <si>
+    <t>0.0105,0.9863,0.0019,0.0022</t>
+  </si>
+  <si>
+    <t>0.0676,0.9608,0.0010,0.0005</t>
+  </si>
+  <si>
+    <t>0.2704,0.8569,0.0022,0.0025</t>
+  </si>
+  <si>
+    <t>0.9552,0.0430,0.0066,0.0021</t>
+  </si>
+  <si>
+    <t>0.5762,0.6014,0.0036,0.0032</t>
+  </si>
+  <si>
+    <t>0.8847,0.0318,0.0803,0.0062</t>
+  </si>
+  <si>
+    <t>0.9535,0.0054,0.0362,0.0056</t>
+  </si>
+  <si>
+    <t>0.9347,0.0100,0.0244,0.0155</t>
+  </si>
+  <si>
+    <t>0.7995,0.0081,0.3153,0.0028</t>
+  </si>
+  <si>
+    <t>0.1870,0.0009,0.7087,0.0235</t>
+  </si>
+  <si>
+    <t>0.0261,0.0057,0.9581,0.0107</t>
+  </si>
+  <si>
+    <t>0.0524,0.0401,0.9043,0.0288</t>
+  </si>
+  <si>
+    <t>0.1817,0.0228,0.8423,0.0170</t>
+  </si>
+  <si>
+    <t>0.1291,0.0078,0.9134,0.0020</t>
+  </si>
+  <si>
+    <t>0.0509,0.0811,0.8059,0.0196</t>
+  </si>
+  <si>
+    <t>0.9974,0.0005,0.0003,0.0006</t>
+  </si>
+  <si>
+    <t>0.9932,0.0027,0.0003,0.0013</t>
+  </si>
+  <si>
+    <t>0.9934,0.0039,0.0004,0.0008</t>
+  </si>
+  <si>
+    <t>0.9984,0.0007,0.0002,0.0001</t>
+  </si>
+  <si>
+    <t>0.9624,0.0503,0.0012,0.0012</t>
+  </si>
+  <si>
+    <t>0.9920,0.0053,0.0009,0.0011</t>
+  </si>
+  <si>
+    <t>0.9974,0.0005,0.0006,0.0006</t>
+  </si>
+  <si>
+    <t>0.9945,0.0008,0.0004,0.0018</t>
+  </si>
+  <si>
+    <t>0.0018,0.0037,0.9980,0.0002</t>
+  </si>
+  <si>
+    <t>0.1734,0.6045,0.1777,0.0025</t>
+  </si>
+  <si>
+    <t>0.9304,0.0081,0.0512,0.0054</t>
+  </si>
+  <si>
+    <t>0.0044,0.0031,0.9973,0.0001</t>
+  </si>
+  <si>
+    <t>0.0004,0.0015,0.9973,0.0041</t>
+  </si>
+  <si>
+    <t>0.0017,0.0481,0.9897,0.0035</t>
+  </si>
+  <si>
+    <t>0.0021,0.0003,0.9986,0.0001</t>
+  </si>
+  <si>
+    <t>0.0178,0.0129,0.9610,0.0142</t>
+  </si>
+  <si>
+    <t>0.0007,0.0010,0.9971,0.0029</t>
+  </si>
+  <si>
+    <t>0.0152,0.0347,0.9658,0.0076</t>
+  </si>
+  <si>
+    <t>0.0536,0.0813,0.8989,0.0096</t>
+  </si>
+  <si>
+    <t>0.8629,0.0053,0.0717,0.0401</t>
+  </si>
+  <si>
+    <t>0.8324,0.0032,0.0791,0.0527</t>
+  </si>
+  <si>
+    <t>0.9421,0.0045,0.0519,0.0059</t>
+  </si>
+  <si>
+    <t>0.9927,0.0033,0.0001,0.0007</t>
+  </si>
+  <si>
+    <t>0.9947,0.0048,0.0004,0.0002</t>
+  </si>
+  <si>
+    <t>0.9952,0.0030,0.0006,0.0005</t>
+  </si>
+  <si>
+    <t>0.9932,0.0039,0.0012,0.0006</t>
+  </si>
+  <si>
+    <t>0.9970,0.0002,0.0001,0.0018</t>
+  </si>
+  <si>
+    <t>0.9909,0.0064,0.0004,0.0006</t>
+  </si>
+  <si>
+    <t>0.9954,0.0017,0.0001,0.0006</t>
+  </si>
+  <si>
+    <t>0.9939,0.0018,0.0009,0.0019</t>
+  </si>
+  <si>
+    <t>0.0161,0.1951,0.9153,0.0019</t>
+  </si>
+  <si>
+    <t>0.0075,0.0605,0.9829,0.0028</t>
+  </si>
+  <si>
+    <t>0.0236,0.0115,0.9663,0.0053</t>
+  </si>
+  <si>
+    <t>0.0141,0.0122,0.9415,0.0267</t>
+  </si>
+  <si>
+    <t>0.0483,0.0025,0.9583,0.0028</t>
+  </si>
+  <si>
+    <t>0.0853,0.0100,0.8847,0.0271</t>
+  </si>
+  <si>
+    <t>0.2631,0.0038,0.7649,0.0107</t>
+  </si>
+  <si>
+    <t>0.0391,0.0012,0.9397,0.0133</t>
+  </si>
+  <si>
+    <t>0.8218,0.0045,0.0196,0.1480</t>
+  </si>
+  <si>
+    <t>0.0053,0.0068,0.0061,0.9929</t>
+  </si>
+  <si>
+    <t>0.0511,0.0002,0.0001,0.9911</t>
+  </si>
+  <si>
+    <t>0.0016,0.0001,0.0002,0.9993</t>
+  </si>
+  <si>
+    <t>0.0018,0.0015,0.0004,0.9989</t>
+  </si>
+  <si>
+    <t>0.9720,0.0051,0.0070,0.0045</t>
   </si>
 </sst>
 </file>
@@ -1967,7 +1967,7 @@
         <v>260</v>
       </c>
       <c r="C3" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D3" t="s">
         <v>265</v>
@@ -1995,7 +1995,7 @@
         <v>260</v>
       </c>
       <c r="C5" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D5" t="s">
         <v>267</v>
@@ -2051,7 +2051,7 @@
         <v>259</v>
       </c>
       <c r="C9" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D9" t="s">
         <v>271</v>
@@ -2107,7 +2107,7 @@
         <v>259</v>
       </c>
       <c r="C13" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D13" t="s">
         <v>275</v>
@@ -2135,7 +2135,7 @@
         <v>261</v>
       </c>
       <c r="C15" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D15" t="s">
         <v>277</v>
@@ -2149,7 +2149,7 @@
         <v>261</v>
       </c>
       <c r="C16" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D16" t="s">
         <v>278</v>
@@ -2163,7 +2163,7 @@
         <v>261</v>
       </c>
       <c r="C17" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D17" t="s">
         <v>279</v>
@@ -2219,7 +2219,7 @@
         <v>262</v>
       </c>
       <c r="C21" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D21" t="s">
         <v>283</v>
@@ -2289,7 +2289,7 @@
         <v>261</v>
       </c>
       <c r="C26" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D26" t="s">
         <v>288</v>
@@ -2303,7 +2303,7 @@
         <v>261</v>
       </c>
       <c r="C27" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D27" t="s">
         <v>289</v>
@@ -2317,7 +2317,7 @@
         <v>261</v>
       </c>
       <c r="C28" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D28" t="s">
         <v>290</v>
@@ -2331,7 +2331,7 @@
         <v>261</v>
       </c>
       <c r="C29" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D29" t="s">
         <v>291</v>
@@ -2359,7 +2359,7 @@
         <v>259</v>
       </c>
       <c r="C31" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D31" t="s">
         <v>293</v>
@@ -2443,7 +2443,7 @@
         <v>259</v>
       </c>
       <c r="C37" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D37" t="s">
         <v>299</v>
@@ -2457,7 +2457,7 @@
         <v>262</v>
       </c>
       <c r="C38" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D38" t="s">
         <v>300</v>
@@ -2471,7 +2471,7 @@
         <v>263</v>
       </c>
       <c r="C39" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D39" t="s">
         <v>301</v>
@@ -2485,7 +2485,7 @@
         <v>261</v>
       </c>
       <c r="C40" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D40" t="s">
         <v>302</v>
@@ -2499,7 +2499,7 @@
         <v>261</v>
       </c>
       <c r="C41" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D41" t="s">
         <v>303</v>
@@ -2513,7 +2513,7 @@
         <v>261</v>
       </c>
       <c r="C42" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D42" t="s">
         <v>304</v>
@@ -2527,7 +2527,7 @@
         <v>263</v>
       </c>
       <c r="C43" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D43" t="s">
         <v>305</v>
@@ -2541,7 +2541,7 @@
         <v>262</v>
       </c>
       <c r="C44" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D44" t="s">
         <v>306</v>
@@ -2555,7 +2555,7 @@
         <v>261</v>
       </c>
       <c r="C45" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D45" t="s">
         <v>307</v>
@@ -2583,7 +2583,7 @@
         <v>262</v>
       </c>
       <c r="C47" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D47" t="s">
         <v>309</v>
@@ -2597,7 +2597,7 @@
         <v>262</v>
       </c>
       <c r="C48" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D48" t="s">
         <v>310</v>
@@ -2611,7 +2611,7 @@
         <v>262</v>
       </c>
       <c r="C49" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D49" t="s">
         <v>311</v>
@@ -2653,7 +2653,7 @@
         <v>261</v>
       </c>
       <c r="C52" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D52" t="s">
         <v>314</v>
@@ -2667,7 +2667,7 @@
         <v>261</v>
       </c>
       <c r="C53" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D53" t="s">
         <v>315</v>
@@ -2681,7 +2681,7 @@
         <v>261</v>
       </c>
       <c r="C54" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D54" t="s">
         <v>316</v>
@@ -2695,7 +2695,7 @@
         <v>261</v>
       </c>
       <c r="C55" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D55" t="s">
         <v>317</v>
@@ -2751,7 +2751,7 @@
         <v>261</v>
       </c>
       <c r="C59" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D59" t="s">
         <v>321</v>
@@ -2807,7 +2807,7 @@
         <v>262</v>
       </c>
       <c r="C63" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D63" t="s">
         <v>325</v>
@@ -2849,7 +2849,7 @@
         <v>263</v>
       </c>
       <c r="C66" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="D66" t="s">
         <v>328</v>
@@ -2877,7 +2877,7 @@
         <v>262</v>
       </c>
       <c r="C68" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D68" t="s">
         <v>330</v>
@@ -2919,7 +2919,7 @@
         <v>261</v>
       </c>
       <c r="C71" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D71" t="s">
         <v>333</v>
@@ -2933,7 +2933,7 @@
         <v>261</v>
       </c>
       <c r="C72" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D72" t="s">
         <v>334</v>
@@ -2947,7 +2947,7 @@
         <v>263</v>
       </c>
       <c r="C73" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="D73" t="s">
         <v>335</v>
@@ -2961,7 +2961,7 @@
         <v>263</v>
       </c>
       <c r="C74" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D74" t="s">
         <v>336</v>
@@ -2975,7 +2975,7 @@
         <v>262</v>
       </c>
       <c r="C75" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="D75" t="s">
         <v>337</v>
@@ -2989,7 +2989,7 @@
         <v>262</v>
       </c>
       <c r="C76" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="D76" t="s">
         <v>338</v>
@@ -3003,7 +3003,7 @@
         <v>260</v>
       </c>
       <c r="C77" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D77" t="s">
         <v>339</v>
@@ -3017,7 +3017,7 @@
         <v>260</v>
       </c>
       <c r="C78" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D78" t="s">
         <v>340</v>
@@ -3031,7 +3031,7 @@
         <v>260</v>
       </c>
       <c r="C79" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D79" t="s">
         <v>341</v>
@@ -3045,7 +3045,7 @@
         <v>260</v>
       </c>
       <c r="C80" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D80" t="s">
         <v>342</v>
@@ -3059,7 +3059,7 @@
         <v>260</v>
       </c>
       <c r="C81" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D81" t="s">
         <v>343</v>
@@ -3073,7 +3073,7 @@
         <v>260</v>
       </c>
       <c r="C82" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D82" t="s">
         <v>344</v>
@@ -3087,7 +3087,7 @@
         <v>263</v>
       </c>
       <c r="C83" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="D83" t="s">
         <v>345</v>
@@ -3115,7 +3115,7 @@
         <v>263</v>
       </c>
       <c r="C85" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D85" t="s">
         <v>347</v>
@@ -3129,7 +3129,7 @@
         <v>263</v>
       </c>
       <c r="C86" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="D86" t="s">
         <v>348</v>
@@ -3143,7 +3143,7 @@
         <v>263</v>
       </c>
       <c r="C87" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="D87" t="s">
         <v>349</v>
@@ -3157,7 +3157,7 @@
         <v>262</v>
       </c>
       <c r="C88" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D88" t="s">
         <v>350</v>
@@ -3171,7 +3171,7 @@
         <v>259</v>
       </c>
       <c r="C89" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D89" t="s">
         <v>351</v>
@@ -3241,7 +3241,7 @@
         <v>259</v>
       </c>
       <c r="C94" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D94" t="s">
         <v>356</v>
@@ -3409,7 +3409,7 @@
         <v>261</v>
       </c>
       <c r="C106" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D106" t="s">
         <v>368</v>
@@ -3437,7 +3437,7 @@
         <v>261</v>
       </c>
       <c r="C108" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D108" t="s">
         <v>370</v>
@@ -3549,7 +3549,7 @@
         <v>259</v>
       </c>
       <c r="C116" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D116" t="s">
         <v>378</v>
@@ -3563,7 +3563,7 @@
         <v>261</v>
       </c>
       <c r="C117" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D117" t="s">
         <v>379</v>
@@ -3591,7 +3591,7 @@
         <v>261</v>
       </c>
       <c r="C119" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D119" t="s">
         <v>381</v>
@@ -3605,7 +3605,7 @@
         <v>262</v>
       </c>
       <c r="C120" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D120" t="s">
         <v>382</v>
@@ -3619,7 +3619,7 @@
         <v>262</v>
       </c>
       <c r="C121" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D121" t="s">
         <v>383</v>
@@ -3633,7 +3633,7 @@
         <v>262</v>
       </c>
       <c r="C122" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D122" t="s">
         <v>384</v>
@@ -3647,7 +3647,7 @@
         <v>262</v>
       </c>
       <c r="C123" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D123" t="s">
         <v>385</v>
@@ -3661,7 +3661,7 @@
         <v>263</v>
       </c>
       <c r="C124" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="D124" t="s">
         <v>386</v>
@@ -3675,7 +3675,7 @@
         <v>262</v>
       </c>
       <c r="C125" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D125" t="s">
         <v>387</v>
@@ -3703,7 +3703,7 @@
         <v>259</v>
       </c>
       <c r="C127" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D127" t="s">
         <v>389</v>
@@ -3829,7 +3829,7 @@
         <v>263</v>
       </c>
       <c r="C136" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D136" t="s">
         <v>398</v>
@@ -3843,7 +3843,7 @@
         <v>261</v>
       </c>
       <c r="C137" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D137" t="s">
         <v>399</v>
@@ -3857,7 +3857,7 @@
         <v>261</v>
       </c>
       <c r="C138" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D138" t="s">
         <v>400</v>
@@ -3871,7 +3871,7 @@
         <v>261</v>
       </c>
       <c r="C139" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D139" t="s">
         <v>401</v>
@@ -3913,7 +3913,7 @@
         <v>261</v>
       </c>
       <c r="C142" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D142" t="s">
         <v>404</v>
@@ -3941,7 +3941,7 @@
         <v>260</v>
       </c>
       <c r="C144" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D144" t="s">
         <v>406</v>
@@ -3955,7 +3955,7 @@
         <v>260</v>
       </c>
       <c r="C145" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D145" t="s">
         <v>407</v>
@@ -3969,7 +3969,7 @@
         <v>260</v>
       </c>
       <c r="C146" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D146" t="s">
         <v>408</v>
@@ -3983,7 +3983,7 @@
         <v>260</v>
       </c>
       <c r="C147" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D147" t="s">
         <v>409</v>
@@ -3997,7 +3997,7 @@
         <v>263</v>
       </c>
       <c r="C148" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="D148" t="s">
         <v>410</v>
@@ -4025,7 +4025,7 @@
         <v>262</v>
       </c>
       <c r="C150" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D150" t="s">
         <v>412</v>
@@ -4053,7 +4053,7 @@
         <v>262</v>
       </c>
       <c r="C152" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D152" t="s">
         <v>414</v>
@@ -4109,7 +4109,7 @@
         <v>261</v>
       </c>
       <c r="C156" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D156" t="s">
         <v>418</v>
@@ -4151,7 +4151,7 @@
         <v>259</v>
       </c>
       <c r="C159" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D159" t="s">
         <v>421</v>
@@ -4193,7 +4193,7 @@
         <v>262</v>
       </c>
       <c r="C162" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D162" t="s">
         <v>424</v>
@@ -4207,7 +4207,7 @@
         <v>259</v>
       </c>
       <c r="C163" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D163" t="s">
         <v>425</v>
@@ -4305,7 +4305,7 @@
         <v>259</v>
       </c>
       <c r="C170" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D170" t="s">
         <v>432</v>
@@ -4375,7 +4375,7 @@
         <v>262</v>
       </c>
       <c r="C175" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D175" t="s">
         <v>437</v>
@@ -4445,7 +4445,7 @@
         <v>259</v>
       </c>
       <c r="C180" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D180" t="s">
         <v>442</v>
@@ -4501,7 +4501,7 @@
         <v>261</v>
       </c>
       <c r="C184" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D184" t="s">
         <v>446</v>
@@ -4515,7 +4515,7 @@
         <v>261</v>
       </c>
       <c r="C185" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D185" t="s">
         <v>447</v>
@@ -4543,7 +4543,7 @@
         <v>261</v>
       </c>
       <c r="C187" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D187" t="s">
         <v>449</v>
@@ -4557,7 +4557,7 @@
         <v>261</v>
       </c>
       <c r="C188" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D188" t="s">
         <v>450</v>
@@ -4571,7 +4571,7 @@
         <v>261</v>
       </c>
       <c r="C189" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D189" t="s">
         <v>451</v>
@@ -4599,7 +4599,7 @@
         <v>259</v>
       </c>
       <c r="C191" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D191" t="s">
         <v>453</v>
@@ -4613,7 +4613,7 @@
         <v>259</v>
       </c>
       <c r="C192" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D192" t="s">
         <v>454</v>
@@ -4641,7 +4641,7 @@
         <v>261</v>
       </c>
       <c r="C194" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D194" t="s">
         <v>456</v>
@@ -4683,7 +4683,7 @@
         <v>259</v>
       </c>
       <c r="C197" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D197" t="s">
         <v>459</v>
@@ -4739,7 +4739,7 @@
         <v>259</v>
       </c>
       <c r="C201" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D201" t="s">
         <v>463</v>
@@ -4753,7 +4753,7 @@
         <v>259</v>
       </c>
       <c r="C202" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D202" t="s">
         <v>464</v>
@@ -4823,7 +4823,7 @@
         <v>259</v>
       </c>
       <c r="C207" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D207" t="s">
         <v>469</v>
@@ -4837,7 +4837,7 @@
         <v>261</v>
       </c>
       <c r="C208" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D208" t="s">
         <v>470</v>
@@ -4851,7 +4851,7 @@
         <v>261</v>
       </c>
       <c r="C209" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D209" t="s">
         <v>471</v>
@@ -4865,7 +4865,7 @@
         <v>261</v>
       </c>
       <c r="C210" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D210" t="s">
         <v>472</v>
@@ -4879,7 +4879,7 @@
         <v>261</v>
       </c>
       <c r="C211" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D211" t="s">
         <v>473</v>
@@ -4893,7 +4893,7 @@
         <v>261</v>
       </c>
       <c r="C212" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D212" t="s">
         <v>474</v>
@@ -5005,7 +5005,7 @@
         <v>259</v>
       </c>
       <c r="C220" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D220" t="s">
         <v>482</v>
@@ -5019,7 +5019,7 @@
         <v>261</v>
       </c>
       <c r="C221" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D221" t="s">
         <v>483</v>
@@ -5033,7 +5033,7 @@
         <v>259</v>
       </c>
       <c r="C222" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D222" t="s">
         <v>484</v>
@@ -5089,7 +5089,7 @@
         <v>261</v>
       </c>
       <c r="C226" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D226" t="s">
         <v>488</v>
@@ -5117,7 +5117,7 @@
         <v>261</v>
       </c>
       <c r="C228" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D228" t="s">
         <v>490</v>
@@ -5145,7 +5145,7 @@
         <v>261</v>
       </c>
       <c r="C230" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D230" t="s">
         <v>492</v>
@@ -5159,7 +5159,7 @@
         <v>261</v>
       </c>
       <c r="C231" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D231" t="s">
         <v>493</v>
@@ -5299,7 +5299,7 @@
         <v>259</v>
       </c>
       <c r="C241" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D241" t="s">
         <v>503</v>
@@ -5327,7 +5327,7 @@
         <v>261</v>
       </c>
       <c r="C243" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D243" t="s">
         <v>505</v>
@@ -5369,7 +5369,7 @@
         <v>261</v>
       </c>
       <c r="C246" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D246" t="s">
         <v>508</v>
@@ -5397,7 +5397,7 @@
         <v>261</v>
       </c>
       <c r="C248" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D248" t="s">
         <v>510</v>
@@ -5411,7 +5411,7 @@
         <v>261</v>
       </c>
       <c r="C249" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D249" t="s">
         <v>511</v>
@@ -5425,7 +5425,7 @@
         <v>261</v>
       </c>
       <c r="C250" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D250" t="s">
         <v>512</v>
@@ -5453,7 +5453,7 @@
         <v>260</v>
       </c>
       <c r="C252" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D252" t="s">
         <v>514</v>
@@ -5467,7 +5467,7 @@
         <v>260</v>
       </c>
       <c r="C253" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D253" t="s">
         <v>515</v>
@@ -5481,7 +5481,7 @@
         <v>260</v>
       </c>
       <c r="C254" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D254" t="s">
         <v>516</v>
@@ -5495,7 +5495,7 @@
         <v>260</v>
       </c>
       <c r="C255" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D255" t="s">
         <v>517</v>
